--- a/Stock_Daily_Reefer_10-8.xlsx
+++ b/Stock_Daily_Reefer_10-8.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOTAL RH" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'TOTAL RH'!$A$1:$Q$59</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -7264,7 +7266,12 @@
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="32" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 

--- a/Stock_Daily_Reefer_10-8.xlsx
+++ b/Stock_Daily_Reefer_10-8.xlsx
@@ -4,17 +4,19 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BookingRaw" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StockRaw" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOTAL RH" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YEAR BUILT" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'TOTAL RH'!$A$1:$Q$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'TOTAL RH'!$A$1:$Q$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'YEAR BUILT'!$A$1:$Q$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -290,39 +292,6 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -361,6 +330,39 @@
       <top style="thin">
         <color rgb="00BFBFBF"/>
       </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="00BFBFBF"/>
       </bottom>
@@ -543,15 +545,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5223,9 +5225,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5266,7 +5268,6 @@
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="n"/>
       <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
     </row>
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="1" t="n"/>
@@ -5304,7 +5305,6 @@
           <t>45RE</t>
         </is>
       </c>
-      <c r="P2" s="1" t="n"/>
     </row>
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -5356,7 +5356,6 @@
         <f>D4</f>
         <v/>
       </c>
-      <c r="P3" s="1" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -5400,7 +5399,6 @@
         <f>J4</f>
         <v/>
       </c>
-      <c r="P4" s="1" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="7">
@@ -5454,7 +5452,6 @@
         <f>SUM(O3:O4)</f>
         <v/>
       </c>
-      <c r="P5" s="1" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="7">
@@ -5496,7 +5493,6 @@
       <c r="M6" s="1" t="n"/>
       <c r="N6" s="1" t="n"/>
       <c r="O6" s="1" t="n"/>
-      <c r="P6" s="1" t="n"/>
     </row>
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="7">
@@ -5550,7 +5546,6 @@
           <t>45RE</t>
         </is>
       </c>
-      <c r="P7" s="1" t="n"/>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="1" t="n"/>
@@ -5596,7 +5591,6 @@
         <f>D5+D6+D7+D9+D11</f>
         <v/>
       </c>
-      <c r="P8" s="1" t="n"/>
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="7">
@@ -5648,7 +5642,6 @@
         <f>J5+J6+J7+J9+J11</f>
         <v/>
       </c>
-      <c r="P9" s="1" t="n"/>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="1" t="n"/>
@@ -5694,7 +5687,6 @@
         <f>SUM(O8:O9)</f>
         <v/>
       </c>
-      <c r="P10" s="1" t="n"/>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="7">
@@ -5736,7 +5728,6 @@
       <c r="M11" s="1" t="n"/>
       <c r="N11" s="1" t="n"/>
       <c r="O11" s="1" t="n"/>
-      <c r="P11" s="1" t="n"/>
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="1" t="n"/>
@@ -5784,7 +5775,6 @@
           <t>45RE</t>
         </is>
       </c>
-      <c r="P12" s="1" t="n"/>
     </row>
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="1" t="n"/>
@@ -5812,7 +5802,6 @@
         <f>D12</f>
         <v/>
       </c>
-      <c r="P13" s="1" t="n"/>
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -5848,7 +5837,6 @@
         <f>J12</f>
         <v/>
       </c>
-      <c r="P14" s="1" t="n"/>
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="1" t="n"/>
@@ -5892,7 +5880,6 @@
         <f>SUM(O13:O14)</f>
         <v/>
       </c>
-      <c r="P15" s="1" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="1" t="n"/>
@@ -5930,7 +5917,6 @@
       <c r="M16" s="1" t="n"/>
       <c r="N16" s="1" t="n"/>
       <c r="O16" s="1" t="n"/>
-      <c r="P16" s="1" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="1" t="n"/>
@@ -5968,7 +5954,6 @@
       <c r="M17" s="1" t="n"/>
       <c r="N17" s="1" t="n"/>
       <c r="O17" s="1" t="n"/>
-      <c r="P17" s="1" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="1" t="n"/>
@@ -5986,7 +5971,6 @@
       <c r="M18" s="1" t="n"/>
       <c r="N18" s="1" t="n"/>
       <c r="O18" s="1" t="n"/>
-      <c r="P18" s="1" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="1" t="n"/>
@@ -6004,7 +5988,6 @@
       <c r="M19" s="1" t="n"/>
       <c r="N19" s="1" t="n"/>
       <c r="O19" s="1" t="n"/>
-      <c r="P19" s="1" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="1" t="n"/>
@@ -6030,7 +6013,6 @@
       <c r="M20" s="1" t="n"/>
       <c r="N20" s="1" t="n"/>
       <c r="O20" s="1" t="n"/>
-      <c r="P20" s="1" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="1" t="n"/>
@@ -6082,7 +6064,6 @@
       <c r="M21" s="1" t="n"/>
       <c r="N21" s="1" t="n"/>
       <c r="O21" s="1" t="n"/>
-      <c r="P21" s="1" t="n"/>
     </row>
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="1" t="n"/>
@@ -6124,7 +6105,6 @@
       <c r="M22" s="1" t="n"/>
       <c r="N22" s="1" t="n"/>
       <c r="O22" s="1" t="n"/>
-      <c r="P22" s="1" t="n"/>
     </row>
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="1" t="n"/>
@@ -6158,7 +6138,6 @@
       <c r="M23" s="1" t="n"/>
       <c r="N23" s="1" t="n"/>
       <c r="O23" s="1" t="n"/>
-      <c r="P23" s="1" t="n"/>
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="1" t="n"/>
@@ -6192,7 +6171,6 @@
       <c r="M24" s="1" t="n"/>
       <c r="N24" s="1" t="n"/>
       <c r="O24" s="1" t="n"/>
-      <c r="P24" s="1" t="n"/>
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="1" t="n"/>
@@ -6226,7 +6204,6 @@
       <c r="M25" s="1" t="n"/>
       <c r="N25" s="1" t="n"/>
       <c r="O25" s="1" t="n"/>
-      <c r="P25" s="1" t="n"/>
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="1" t="n"/>
@@ -6260,7 +6237,6 @@
       <c r="M26" s="1" t="n"/>
       <c r="N26" s="1" t="n"/>
       <c r="O26" s="1" t="n"/>
-      <c r="P26" s="1" t="n"/>
     </row>
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="1" t="n"/>
@@ -6294,7 +6270,6 @@
       <c r="M27" s="1" t="n"/>
       <c r="N27" s="1" t="n"/>
       <c r="O27" s="1" t="n"/>
-      <c r="P27" s="1" t="n"/>
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="1" t="n"/>
@@ -6328,7 +6303,6 @@
       <c r="M28" s="1" t="n"/>
       <c r="N28" s="1" t="n"/>
       <c r="O28" s="1" t="n"/>
-      <c r="P28" s="1" t="n"/>
     </row>
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="1" t="n"/>
@@ -6366,7 +6340,6 @@
       <c r="M29" s="1" t="n"/>
       <c r="N29" s="1" t="n"/>
       <c r="O29" s="1" t="n"/>
-      <c r="P29" s="1" t="n"/>
     </row>
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="1" t="n"/>
@@ -6396,886 +6369,883 @@
       <c r="M30" s="1" t="n"/>
       <c r="N30" s="1" t="n"/>
       <c r="O30" s="1" t="n"/>
-      <c r="P30" s="1" t="n"/>
-    </row>
-    <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="n"/>
-      <c r="C31" s="1" t="n"/>
-      <c r="D31" s="1" t="n"/>
-      <c r="E31" s="1" t="n"/>
-      <c r="F31" s="1" t="n"/>
-      <c r="G31" s="1" t="n"/>
-      <c r="H31" s="1" t="n"/>
-      <c r="I31" s="1" t="n"/>
-      <c r="J31" s="1" t="n"/>
-      <c r="K31" s="1" t="n"/>
-      <c r="L31" s="1" t="n"/>
-      <c r="M31" s="1" t="n"/>
-      <c r="N31" s="1" t="n"/>
-      <c r="O31" s="1" t="n"/>
-      <c r="P31" s="1" t="n"/>
-    </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="1" t="n"/>
-      <c r="B32" s="1" t="n"/>
-      <c r="C32" s="1" t="n"/>
-      <c r="D32" s="1" t="n"/>
-      <c r="E32" s="1" t="n"/>
-      <c r="F32" s="1" t="n"/>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="1" t="n"/>
-      <c r="I32" s="1" t="n"/>
-      <c r="J32" s="1" t="n"/>
-      <c r="K32" s="1" t="n"/>
-      <c r="L32" s="1" t="n"/>
-      <c r="M32" s="1" t="n"/>
-      <c r="N32" s="1" t="n"/>
-      <c r="O32" s="1" t="n"/>
-      <c r="P32" s="1" t="n"/>
-    </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="1" t="n"/>
-      <c r="B33" s="21" t="inlineStr">
-        <is>
-          <t>CARGO CLASSIFICATION  (40'RH stock by Built Year, per depot)</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="n"/>
-      <c r="D33" s="1" t="n"/>
-      <c r="E33" s="1" t="n"/>
-      <c r="F33" s="1" t="n"/>
-      <c r="G33" s="1" t="n"/>
-      <c r="H33" s="1" t="n"/>
-      <c r="I33" s="1" t="n"/>
-      <c r="J33" s="1" t="n"/>
-      <c r="K33" s="1" t="n"/>
-      <c r="L33" s="1" t="n"/>
-      <c r="M33" s="1" t="n"/>
-      <c r="N33" s="1" t="n"/>
-      <c r="O33" s="1" t="n"/>
-      <c r="P33" s="1" t="n"/>
-    </row>
-    <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="1" t="n"/>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>BKK27 DURIAN  (2021-2026)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="1" t="n"/>
-      <c r="F34" s="22" t="inlineStr">
-        <is>
-          <t>BKK27 NON DURIAN  (≤ 2020)</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="n"/>
-      <c r="H34" s="23" t="n"/>
-      <c r="I34" s="1" t="n"/>
-      <c r="J34" s="22" t="inlineStr">
-        <is>
-          <t>LCH27 DURIAN  (2021-2026)</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n"/>
-      <c r="L34" s="23" t="n"/>
-      <c r="M34" s="1" t="n"/>
-      <c r="N34" s="22" t="inlineStr">
-        <is>
-          <t>LCH27 NON DURIAN  (≤ 2020)</t>
-        </is>
-      </c>
-      <c r="O34" s="23" t="n"/>
-      <c r="P34" s="23" t="n"/>
-    </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="24">
-        <f>SUM(D42:D47)+SUM(F42:F47)+SUM(H42:H47)</f>
-        <v/>
-      </c>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="1" t="n"/>
-      <c r="F35" s="24">
-        <f>SUM(D48:D58)+SUM(F48:F58)+SUM(H48:H58)</f>
-        <v/>
-      </c>
-      <c r="G35" s="23" t="n"/>
-      <c r="H35" s="23" t="n"/>
-      <c r="I35" s="1" t="n"/>
-      <c r="J35" s="25">
-        <f>SUM(L42:L47)+SUM(N42:N47)+SUM(P42:P47)</f>
-        <v/>
-      </c>
-      <c r="K35" s="23" t="n"/>
-      <c r="L35" s="23" t="n"/>
-      <c r="M35" s="1" t="n"/>
-      <c r="N35" s="25">
-        <f>SUM(L48:L58)+SUM(N48:N58)+SUM(P48:P58)</f>
-        <v/>
-      </c>
-      <c r="O35" s="23" t="n"/>
-      <c r="P35" s="23" t="n"/>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="1" t="n"/>
-      <c r="F36" s="26" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="n"/>
-      <c r="H36" s="23" t="n"/>
-      <c r="I36" s="1" t="n"/>
-      <c r="J36" s="26" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n"/>
-      <c r="L36" s="23" t="n"/>
-      <c r="M36" s="1" t="n"/>
-      <c r="N36" s="26" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="O36" s="23" t="n"/>
-      <c r="P36" s="23" t="n"/>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="1" t="n"/>
-      <c r="C37" s="1" t="n"/>
-      <c r="D37" s="1" t="n"/>
-      <c r="E37" s="1" t="n"/>
-      <c r="F37" s="1" t="n"/>
-      <c r="G37" s="1" t="n"/>
-      <c r="H37" s="1" t="n"/>
-      <c r="I37" s="1" t="n"/>
-      <c r="J37" s="1" t="n"/>
-      <c r="K37" s="1" t="n"/>
-      <c r="L37" s="1" t="n"/>
-      <c r="M37" s="1" t="n"/>
-      <c r="N37" s="1" t="n"/>
-      <c r="O37" s="1" t="n"/>
-      <c r="P37" s="1" t="n"/>
-    </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="1" t="n"/>
-      <c r="C38" s="1" t="n"/>
-      <c r="D38" s="1" t="n"/>
-      <c r="E38" s="1" t="n"/>
-      <c r="F38" s="1" t="n"/>
-      <c r="G38" s="1" t="n"/>
-      <c r="H38" s="1" t="n"/>
-      <c r="I38" s="1" t="n"/>
-      <c r="J38" s="1" t="n"/>
-      <c r="K38" s="1" t="n"/>
-      <c r="L38" s="1" t="n"/>
-      <c r="M38" s="1" t="n"/>
-      <c r="N38" s="1" t="n"/>
-      <c r="O38" s="1" t="n"/>
-      <c r="P38" s="1" t="n"/>
-    </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>BKK27 / BC2  —  Stock by Built Year x Brand x Size</t>
-        </is>
-      </c>
-      <c r="C39" s="56" t="n"/>
-      <c r="D39" s="56" t="n"/>
-      <c r="E39" s="56" t="n"/>
-      <c r="F39" s="56" t="n"/>
-      <c r="G39" s="56" t="n"/>
-      <c r="H39" s="57" t="n"/>
-      <c r="I39" s="1" t="n"/>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LCH27 / HAST  —  Stock by Built Year x Brand x Size</t>
-        </is>
-      </c>
-      <c r="K39" s="56" t="n"/>
-      <c r="L39" s="56" t="n"/>
-      <c r="M39" s="56" t="n"/>
-      <c r="N39" s="56" t="n"/>
-      <c r="O39" s="56" t="n"/>
-      <c r="P39" s="57" t="n"/>
-    </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>YEAR
-BUILT</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>CARRIER</t>
-        </is>
-      </c>
-      <c r="D40" s="57" t="n"/>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>DAIKIN</t>
-        </is>
-      </c>
-      <c r="F40" s="57" t="n"/>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>THERMO KING</t>
-        </is>
-      </c>
-      <c r="H40" s="57" t="n"/>
-      <c r="I40" s="1" t="n"/>
-      <c r="J40" s="18" t="inlineStr">
-        <is>
-          <t>YEAR
-BUILT</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>CARRIER</t>
-        </is>
-      </c>
-      <c r="L40" s="57" t="n"/>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>DAIKIN</t>
-        </is>
-      </c>
-      <c r="N40" s="57" t="n"/>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>THERMO KING</t>
-        </is>
-      </c>
-      <c r="P40" s="57" t="n"/>
-    </row>
-    <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="60" t="n"/>
-      <c r="C41" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="D41" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="E41" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="F41" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="G41" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="H41" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="I41" s="1" t="n"/>
-      <c r="J41" s="60" t="n"/>
-      <c r="K41" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="L41" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="M41" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="N41" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="O41" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="P41" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="13" customHeight="1">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C42" s="30" t="n"/>
-      <c r="D42" s="30" t="n"/>
-      <c r="E42" s="30" t="n"/>
-      <c r="F42" s="30" t="n"/>
-      <c r="G42" s="30" t="n"/>
-      <c r="H42" s="30" t="n"/>
-      <c r="I42" s="1" t="n"/>
-      <c r="J42" s="29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="K42" s="30" t="n"/>
-      <c r="L42" s="30" t="n"/>
-      <c r="M42" s="30" t="n"/>
-      <c r="N42" s="30" t="n"/>
-      <c r="O42" s="30" t="n"/>
-      <c r="P42" s="30" t="n"/>
-    </row>
-    <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="29" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" s="30" t="n"/>
-      <c r="G43" s="30" t="n"/>
-      <c r="H43" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="1" t="n"/>
-      <c r="J43" s="29" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K43" s="30" t="n"/>
-      <c r="L43" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="M43" s="30" t="n"/>
-      <c r="N43" s="30" t="n"/>
-      <c r="O43" s="30" t="n"/>
-      <c r="P43" s="30" t="n"/>
-    </row>
-    <row r="44" ht="13" customHeight="1">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C44" s="30" t="n"/>
-      <c r="D44" s="30" t="n"/>
-      <c r="E44" s="30" t="n"/>
-      <c r="F44" s="30" t="n"/>
-      <c r="G44" s="30" t="n"/>
-      <c r="H44" s="30" t="n"/>
-      <c r="I44" s="1" t="n"/>
-      <c r="J44" s="29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="K44" s="30" t="n"/>
-      <c r="L44" s="30" t="n"/>
-      <c r="M44" s="30" t="n"/>
-      <c r="N44" s="30" t="n"/>
-      <c r="O44" s="30" t="n"/>
-      <c r="P44" s="30" t="n"/>
-    </row>
-    <row r="45" ht="13" customHeight="1">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="29" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="30" t="n"/>
-      <c r="F45" s="30" t="n"/>
-      <c r="G45" s="30" t="n"/>
-      <c r="H45" s="30" t="n"/>
-      <c r="I45" s="1" t="n"/>
-      <c r="J45" s="29" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K45" s="30" t="n"/>
-      <c r="L45" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="M45" s="30" t="n"/>
-      <c r="N45" s="30" t="n"/>
-      <c r="O45" s="30" t="n"/>
-      <c r="P45" s="30" t="n"/>
-    </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="1" t="n"/>
-      <c r="B46" s="29" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C46" s="30" t="n"/>
-      <c r="D46" s="30" t="n"/>
-      <c r="E46" s="30" t="n"/>
-      <c r="F46" s="30" t="n"/>
-      <c r="G46" s="30" t="n"/>
-      <c r="H46" s="30" t="n"/>
-      <c r="I46" s="1" t="n"/>
-      <c r="J46" s="29" t="n">
-        <v>2022</v>
-      </c>
-      <c r="K46" s="30" t="n"/>
-      <c r="L46" s="30" t="n"/>
-      <c r="M46" s="30" t="n"/>
-      <c r="N46" s="30" t="n"/>
-      <c r="O46" s="30" t="n"/>
-      <c r="P46" s="30" t="n"/>
-    </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="29" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C47" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="D47" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="E47" s="30" t="n"/>
-      <c r="F47" s="30" t="n"/>
-      <c r="G47" s="30" t="n"/>
-      <c r="H47" s="30" t="n"/>
-      <c r="I47" s="1" t="n"/>
-      <c r="J47" s="29" t="n">
-        <v>2021</v>
-      </c>
-      <c r="K47" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="M47" s="30" t="n"/>
-      <c r="N47" s="30" t="n"/>
-      <c r="O47" s="30" t="n"/>
-      <c r="P47" s="30" t="n"/>
-    </row>
-    <row r="48" ht="13" customHeight="1">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="31" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C48" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E48" s="32" t="n"/>
-      <c r="F48" s="32" t="n"/>
-      <c r="G48" s="32" t="n"/>
-      <c r="H48" s="32" t="n"/>
-      <c r="I48" s="1" t="n"/>
-      <c r="J48" s="31" t="n">
-        <v>2020</v>
-      </c>
-      <c r="K48" s="32" t="n"/>
-      <c r="L48" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="M48" s="32" t="n"/>
-      <c r="N48" s="32" t="n"/>
-      <c r="O48" s="32" t="n"/>
-      <c r="P48" s="32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="31" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C49" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E49" s="32" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="32" t="n"/>
-      <c r="H49" s="32" t="n"/>
-      <c r="I49" s="1" t="n"/>
-      <c r="J49" s="31" t="n">
-        <v>2019</v>
-      </c>
-      <c r="K49" s="32" t="n"/>
-      <c r="L49" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="M49" s="32" t="n"/>
-      <c r="N49" s="32" t="n"/>
-      <c r="O49" s="32" t="n"/>
-      <c r="P49" s="32" t="n"/>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="31" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C50" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="32" t="n"/>
-      <c r="E50" s="32" t="n"/>
-      <c r="F50" s="32" t="n"/>
-      <c r="G50" s="32" t="n"/>
-      <c r="H50" s="32" t="n"/>
-      <c r="I50" s="1" t="n"/>
-      <c r="J50" s="31" t="n">
-        <v>2018</v>
-      </c>
-      <c r="K50" s="32" t="n"/>
-      <c r="L50" s="32" t="n"/>
-      <c r="M50" s="32" t="n"/>
-      <c r="N50" s="32" t="n"/>
-      <c r="O50" s="32" t="n"/>
-      <c r="P50" s="32" t="n"/>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="31" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C51" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
-      <c r="H51" s="32" t="n"/>
-      <c r="I51" s="1" t="n"/>
-      <c r="J51" s="31" t="n">
-        <v>2017</v>
-      </c>
-      <c r="K51" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L51" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="M51" s="32" t="n"/>
-      <c r="N51" s="32" t="n"/>
-      <c r="O51" s="32" t="n"/>
-      <c r="P51" s="32" t="n"/>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="31" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C52" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" s="32" t="n"/>
-      <c r="G52" s="32" t="n"/>
-      <c r="H52" s="32" t="n"/>
-      <c r="I52" s="1" t="n"/>
-      <c r="J52" s="31" t="n">
-        <v>2016</v>
-      </c>
-      <c r="K52" s="32" t="n"/>
-      <c r="L52" s="32" t="n"/>
-      <c r="M52" s="32" t="n"/>
-      <c r="N52" s="32" t="n"/>
-      <c r="O52" s="32" t="n"/>
-      <c r="P52" s="32" t="n"/>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="33" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C53" s="34" t="n"/>
-      <c r="D53" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="E53" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="F53" s="34" t="n"/>
-      <c r="G53" s="34" t="n"/>
-      <c r="H53" s="34" t="n"/>
-      <c r="I53" s="1" t="n"/>
-      <c r="J53" s="33" t="n">
-        <v>2015</v>
-      </c>
-      <c r="K53" s="34" t="n"/>
-      <c r="L53" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" s="34" t="n"/>
-      <c r="N53" s="34" t="n"/>
-      <c r="O53" s="34" t="n"/>
-      <c r="P53" s="34" t="n"/>
-    </row>
-    <row r="54" ht="13" customHeight="1">
-      <c r="A54" s="1" t="n"/>
-      <c r="B54" s="33" t="n">
-        <v>2014</v>
-      </c>
-      <c r="C54" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D54" s="34" t="n"/>
-      <c r="E54" s="34" t="n"/>
-      <c r="F54" s="34" t="n"/>
-      <c r="G54" s="34" t="n"/>
-      <c r="H54" s="34" t="n"/>
-      <c r="I54" s="1" t="n"/>
-      <c r="J54" s="33" t="n">
-        <v>2014</v>
-      </c>
-      <c r="K54" s="34" t="n"/>
-      <c r="L54" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="M54" s="34" t="n"/>
-      <c r="N54" s="34" t="n"/>
-      <c r="O54" s="34" t="n"/>
-      <c r="P54" s="34" t="n"/>
-    </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="33" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C55" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="34" t="n"/>
-      <c r="E55" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="1" t="n"/>
-      <c r="J55" s="33" t="n">
-        <v>2013</v>
-      </c>
-      <c r="K55" s="34" t="n"/>
-      <c r="L55" s="34" t="n"/>
-      <c r="M55" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N55" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="O55" s="34" t="n"/>
-      <c r="P55" s="34" t="n"/>
-    </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="1" t="n"/>
-      <c r="B56" s="33" t="n">
-        <v>2012</v>
-      </c>
-      <c r="C56" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" s="34" t="n"/>
-      <c r="F56" s="34" t="n"/>
-      <c r="G56" s="34" t="n"/>
-      <c r="H56" s="34" t="n"/>
-      <c r="I56" s="1" t="n"/>
-      <c r="J56" s="33" t="n">
-        <v>2012</v>
-      </c>
-      <c r="K56" s="34" t="n"/>
-      <c r="L56" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="M56" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" s="34" t="n"/>
-      <c r="O56" s="34" t="n"/>
-      <c r="P56" s="34" t="n"/>
-    </row>
-    <row r="57" ht="13" customHeight="1">
-      <c r="A57" s="1" t="n"/>
-      <c r="B57" s="33" t="n">
-        <v>2011</v>
-      </c>
-      <c r="C57" s="34" t="n"/>
-      <c r="D57" s="34" t="n"/>
-      <c r="E57" s="34" t="n"/>
-      <c r="F57" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" s="34" t="n"/>
-      <c r="H57" s="34" t="n"/>
-      <c r="I57" s="1" t="n"/>
-      <c r="J57" s="33" t="n">
-        <v>2011</v>
-      </c>
-      <c r="K57" s="34" t="n"/>
-      <c r="L57" s="34" t="n"/>
-      <c r="M57" s="34" t="n"/>
-      <c r="N57" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O57" s="34" t="n"/>
-      <c r="P57" s="34" t="n"/>
-    </row>
-    <row r="58" ht="13" customHeight="1">
-      <c r="A58" s="1" t="n"/>
-      <c r="B58" s="35" t="n">
-        <v>2010</v>
-      </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
-      <c r="I58" s="1" t="n"/>
-      <c r="J58" s="35" t="n">
-        <v>2010</v>
-      </c>
-      <c r="K58" s="36" t="n"/>
-      <c r="L58" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" s="36" t="n"/>
-      <c r="N58" s="36" t="n"/>
-      <c r="O58" s="36" t="n"/>
-      <c r="P58" s="36" t="n"/>
-    </row>
-    <row r="59" ht="13" customHeight="1">
-      <c r="A59" s="1" t="n"/>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>GTTL</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="D59" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="E59" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F59" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G59" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I59" s="1" t="n"/>
-      <c r="J59" s="13" t="inlineStr">
-        <is>
-          <t>GTTL</t>
-        </is>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="O59" s="13" t="n"/>
-      <c r="P59" s="13" t="n">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="J39:P39"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="O40:P40"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="H20:K20"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="E40:F40"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H21:H22"/>
-    <mergeCell ref="C40:D40"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="K40:L40"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="32" min="0" max="16383" man="1"/>
-  </rowBreaks>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="13" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>CARGO CLASSIFICATION  (40'RH stock by Built Year, per depot)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>BKK27 DURIAN  (2021-2026)</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="n"/>
+      <c r="D2" s="23" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
+          <t>BKK27 NON DURIAN  (≤ 2020)</t>
+        </is>
+      </c>
+      <c r="G2" s="23" t="n"/>
+      <c r="H2" s="23" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="22" t="inlineStr">
+        <is>
+          <t>LCH27 DURIAN  (2021-2026)</t>
+        </is>
+      </c>
+      <c r="K2" s="23" t="n"/>
+      <c r="L2" s="23" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="22" t="inlineStr">
+        <is>
+          <t>LCH27 NON DURIAN  (≤ 2020)</t>
+        </is>
+      </c>
+      <c r="O2" s="23" t="n"/>
+      <c r="P2" s="23" t="n"/>
+    </row>
+    <row r="3" ht="13" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="24">
+        <f>SUM(D10:D15)+SUM(F10:F15)+SUM(H10:H15)</f>
+        <v/>
+      </c>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="24">
+        <f>SUM(D16:D26)+SUM(F16:F26)+SUM(H16:H26)</f>
+        <v/>
+      </c>
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="23" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="25">
+        <f>SUM(L10:L15)+SUM(N10:N15)+SUM(P10:P15)</f>
+        <v/>
+      </c>
+      <c r="K3" s="23" t="n"/>
+      <c r="L3" s="23" t="n"/>
+      <c r="M3" s="1" t="n"/>
+      <c r="N3" s="25">
+        <f>SUM(L16:L26)+SUM(N16:N26)+SUM(P16:P26)</f>
+        <v/>
+      </c>
+      <c r="O3" s="23" t="n"/>
+      <c r="P3" s="23" t="n"/>
+    </row>
+    <row r="4" ht="13" customHeight="1">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="n"/>
+      <c r="D4" s="23" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="n"/>
+      <c r="H4" s="23" t="n"/>
+      <c r="I4" s="1" t="n"/>
+      <c r="J4" s="26" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="K4" s="23" t="n"/>
+      <c r="L4" s="23" t="n"/>
+      <c r="M4" s="1" t="n"/>
+      <c r="N4" s="26" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
+      <c r="I5" s="1" t="n"/>
+      <c r="J5" s="1" t="n"/>
+      <c r="K5" s="1" t="n"/>
+      <c r="L5" s="1" t="n"/>
+      <c r="M5" s="1" t="n"/>
+      <c r="N5" s="1" t="n"/>
+      <c r="O5" s="1" t="n"/>
+      <c r="P5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="n"/>
+      <c r="M6" s="1" t="n"/>
+      <c r="N6" s="1" t="n"/>
+      <c r="O6" s="1" t="n"/>
+      <c r="P6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="13" customHeight="1">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>BKK27 / BC2  —  Stock by Built Year x Brand x Size</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="n"/>
+      <c r="D7" s="56" t="n"/>
+      <c r="E7" s="56" t="n"/>
+      <c r="F7" s="56" t="n"/>
+      <c r="G7" s="56" t="n"/>
+      <c r="H7" s="57" t="n"/>
+      <c r="I7" s="1" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LCH27 / HAST  —  Stock by Built Year x Brand x Size</t>
+        </is>
+      </c>
+      <c r="K7" s="56" t="n"/>
+      <c r="L7" s="56" t="n"/>
+      <c r="M7" s="56" t="n"/>
+      <c r="N7" s="56" t="n"/>
+      <c r="O7" s="56" t="n"/>
+      <c r="P7" s="57" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>YEAR
+BUILT</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CARRIER</t>
+        </is>
+      </c>
+      <c r="D8" s="57" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>DAIKIN</t>
+        </is>
+      </c>
+      <c r="F8" s="57" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>THERMO KING</t>
+        </is>
+      </c>
+      <c r="H8" s="57" t="n"/>
+      <c r="I8" s="1" t="n"/>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>YEAR
+BUILT</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>CARRIER</t>
+        </is>
+      </c>
+      <c r="L8" s="57" t="n"/>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>DAIKIN</t>
+        </is>
+      </c>
+      <c r="N8" s="57" t="n"/>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>THERMO KING</t>
+        </is>
+      </c>
+      <c r="P8" s="57" t="n"/>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="60" t="n"/>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="n"/>
+      <c r="J9" s="60" t="n"/>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="L9" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="M9" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="N9" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="O9" s="28" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="P9" s="28" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="30" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+      <c r="H10" s="30" t="n"/>
+      <c r="I10" s="1" t="n"/>
+      <c r="J10" s="29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K10" s="30" t="n"/>
+      <c r="L10" s="30" t="n"/>
+      <c r="M10" s="30" t="n"/>
+      <c r="N10" s="30" t="n"/>
+      <c r="O10" s="30" t="n"/>
+      <c r="P10" s="30" t="n"/>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="n"/>
+      <c r="J11" s="29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K11" s="30" t="n"/>
+      <c r="L11" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" s="30" t="n"/>
+      <c r="N11" s="30" t="n"/>
+      <c r="O11" s="30" t="n"/>
+      <c r="P11" s="30" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+      <c r="H12" s="30" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K12" s="30" t="n"/>
+      <c r="L12" s="30" t="n"/>
+      <c r="M12" s="30" t="n"/>
+      <c r="N12" s="30" t="n"/>
+      <c r="O12" s="30" t="n"/>
+      <c r="P12" s="30" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="30" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+      <c r="H13" s="30" t="n"/>
+      <c r="I13" s="1" t="n"/>
+      <c r="J13" s="29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K13" s="30" t="n"/>
+      <c r="L13" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="30" t="n"/>
+      <c r="N13" s="30" t="n"/>
+      <c r="O13" s="30" t="n"/>
+      <c r="P13" s="30" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="30" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+      <c r="H14" s="30" t="n"/>
+      <c r="I14" s="1" t="n"/>
+      <c r="J14" s="29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="K14" s="30" t="n"/>
+      <c r="L14" s="30" t="n"/>
+      <c r="M14" s="30" t="n"/>
+      <c r="N14" s="30" t="n"/>
+      <c r="O14" s="30" t="n"/>
+      <c r="P14" s="30" t="n"/>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="29" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+      <c r="H15" s="30" t="n"/>
+      <c r="I15" s="1" t="n"/>
+      <c r="J15" s="29" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" s="30" t="n"/>
+      <c r="N15" s="30" t="n"/>
+      <c r="O15" s="30" t="n"/>
+      <c r="P15" s="30" t="n"/>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="31" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C16" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="32" t="n"/>
+      <c r="H16" s="32" t="n"/>
+      <c r="I16" s="1" t="n"/>
+      <c r="J16" s="31" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K16" s="32" t="n"/>
+      <c r="L16" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="M16" s="32" t="n"/>
+      <c r="N16" s="32" t="n"/>
+      <c r="O16" s="32" t="n"/>
+      <c r="P16" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="31" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C17" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="32" t="n"/>
+      <c r="H17" s="32" t="n"/>
+      <c r="I17" s="1" t="n"/>
+      <c r="J17" s="31" t="n">
+        <v>2019</v>
+      </c>
+      <c r="K17" s="32" t="n"/>
+      <c r="L17" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="M17" s="32" t="n"/>
+      <c r="N17" s="32" t="n"/>
+      <c r="O17" s="32" t="n"/>
+      <c r="P17" s="32" t="n"/>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C18" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="32" t="n"/>
+      <c r="H18" s="32" t="n"/>
+      <c r="I18" s="1" t="n"/>
+      <c r="J18" s="31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K18" s="32" t="n"/>
+      <c r="L18" s="32" t="n"/>
+      <c r="M18" s="32" t="n"/>
+      <c r="N18" s="32" t="n"/>
+      <c r="O18" s="32" t="n"/>
+      <c r="P18" s="32" t="n"/>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="31" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="1" t="n"/>
+      <c r="J19" s="31" t="n">
+        <v>2017</v>
+      </c>
+      <c r="K19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="32" t="n"/>
+      <c r="N19" s="32" t="n"/>
+      <c r="O19" s="32" t="n"/>
+      <c r="P19" s="32" t="n"/>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="31" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="32" t="n"/>
+      <c r="H20" s="32" t="n"/>
+      <c r="I20" s="1" t="n"/>
+      <c r="J20" s="31" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K20" s="32" t="n"/>
+      <c r="L20" s="32" t="n"/>
+      <c r="M20" s="32" t="n"/>
+      <c r="N20" s="32" t="n"/>
+      <c r="O20" s="32" t="n"/>
+      <c r="P20" s="32" t="n"/>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="33" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C21" s="34" t="n"/>
+      <c r="D21" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="34" t="n"/>
+      <c r="G21" s="34" t="n"/>
+      <c r="H21" s="34" t="n"/>
+      <c r="I21" s="1" t="n"/>
+      <c r="J21" s="33" t="n">
+        <v>2015</v>
+      </c>
+      <c r="K21" s="34" t="n"/>
+      <c r="L21" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" s="34" t="n"/>
+      <c r="N21" s="34" t="n"/>
+      <c r="O21" s="34" t="n"/>
+      <c r="P21" s="34" t="n"/>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="33" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="34" t="n"/>
+      <c r="H22" s="34" t="n"/>
+      <c r="I22" s="1" t="n"/>
+      <c r="J22" s="33" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K22" s="34" t="n"/>
+      <c r="L22" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" s="34" t="n"/>
+      <c r="N22" s="34" t="n"/>
+      <c r="O22" s="34" t="n"/>
+      <c r="P22" s="34" t="n"/>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="33" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="34" t="n"/>
+      <c r="E23" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="n"/>
+      <c r="J23" s="33" t="n">
+        <v>2013</v>
+      </c>
+      <c r="K23" s="34" t="n"/>
+      <c r="L23" s="34" t="n"/>
+      <c r="M23" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" s="34" t="n"/>
+      <c r="P23" s="34" t="n"/>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="33" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="34" t="n"/>
+      <c r="G24" s="34" t="n"/>
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="1" t="n"/>
+      <c r="J24" s="33" t="n">
+        <v>2012</v>
+      </c>
+      <c r="K24" s="34" t="n"/>
+      <c r="L24" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="34" t="n"/>
+      <c r="O24" s="34" t="n"/>
+      <c r="P24" s="34" t="n"/>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="33" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="34" t="n"/>
+      <c r="E25" s="34" t="n"/>
+      <c r="F25" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="34" t="n"/>
+      <c r="H25" s="34" t="n"/>
+      <c r="I25" s="1" t="n"/>
+      <c r="J25" s="33" t="n">
+        <v>2011</v>
+      </c>
+      <c r="K25" s="34" t="n"/>
+      <c r="L25" s="34" t="n"/>
+      <c r="M25" s="34" t="n"/>
+      <c r="N25" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" s="34" t="n"/>
+      <c r="P25" s="34" t="n"/>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="1" t="n"/>
+      <c r="J26" s="35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="K26" s="36" t="n"/>
+      <c r="L26" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="36" t="n"/>
+      <c r="N26" s="36" t="n"/>
+      <c r="O26" s="36" t="n"/>
+      <c r="P26" s="36" t="n"/>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>GTTL</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="1" t="n"/>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>GTTL</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O27" s="13" t="n"/>
+      <c r="P27" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="O8:P8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8158,14 +8128,14 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="53">
-        <f>SUM('TOTAL RH'!D42:D48)+SUM('TOTAL RH'!F42:F48)+SUM('TOTAL RH'!H42:H48)</f>
+        <f>SUM('YEAR BUILT'!D10:D16)+SUM('YEAR BUILT'!F10:F16)+SUM('YEAR BUILT'!H10:H16)</f>
         <v/>
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="23" t="n"/>
       <c r="E33" s="1" t="n"/>
       <c r="F33" s="54">
-        <f>SUM('TOTAL RH'!L42:L48)+SUM('TOTAL RH'!N42:N48)+SUM('TOTAL RH'!P42:P48)</f>
+        <f>SUM('YEAR BUILT'!L10:L16)+SUM('YEAR BUILT'!N10:N16)+SUM('YEAR BUILT'!P10:P16)</f>
         <v/>
       </c>
       <c r="G33" s="23" t="n"/>
@@ -8267,28 +8237,28 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="53">
-        <f>'TOTAL RH'!B35</f>
+        <f>'YEAR BUILT'!B3</f>
         <v/>
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="1" t="n"/>
       <c r="F37" s="53">
-        <f>'TOTAL RH'!F35</f>
+        <f>'YEAR BUILT'!F3</f>
         <v/>
       </c>
       <c r="G37" s="23" t="n"/>
       <c r="H37" s="23" t="n"/>
       <c r="I37" s="1" t="n"/>
       <c r="J37" s="54">
-        <f>'TOTAL RH'!J35</f>
+        <f>'YEAR BUILT'!J3</f>
         <v/>
       </c>
       <c r="K37" s="23" t="n"/>
       <c r="L37" s="23" t="n"/>
       <c r="M37" s="1" t="n"/>
       <c r="N37" s="54">
-        <f>'TOTAL RH'!N35</f>
+        <f>'YEAR BUILT'!N3</f>
         <v/>
       </c>
       <c r="O37" s="23" t="n"/>
@@ -8414,11 +8384,11 @@
         </is>
       </c>
       <c r="C42" s="50">
-        <f>'TOTAL RH'!C59</f>
+        <f>'YEAR BUILT'!C27</f>
         <v/>
       </c>
       <c r="D42" s="50">
-        <f>'TOTAL RH'!D59</f>
+        <f>'YEAR BUILT'!D27</f>
         <v/>
       </c>
       <c r="E42" s="1" t="n"/>
@@ -8430,11 +8400,11 @@
         </is>
       </c>
       <c r="I42" s="50">
-        <f>'TOTAL RH'!K59</f>
+        <f>'YEAR BUILT'!K27</f>
         <v/>
       </c>
       <c r="J42" s="50">
-        <f>'TOTAL RH'!L59</f>
+        <f>'YEAR BUILT'!L27</f>
         <v/>
       </c>
       <c r="K42" s="1" t="n"/>
@@ -8452,11 +8422,11 @@
         </is>
       </c>
       <c r="C43" s="50">
-        <f>'TOTAL RH'!E59</f>
+        <f>'YEAR BUILT'!E27</f>
         <v/>
       </c>
       <c r="D43" s="50">
-        <f>'TOTAL RH'!F59</f>
+        <f>'YEAR BUILT'!F27</f>
         <v/>
       </c>
       <c r="E43" s="1" t="n"/>
@@ -8468,11 +8438,11 @@
         </is>
       </c>
       <c r="I43" s="50">
-        <f>'TOTAL RH'!M59</f>
+        <f>'YEAR BUILT'!M27</f>
         <v/>
       </c>
       <c r="J43" s="50">
-        <f>'TOTAL RH'!N59</f>
+        <f>'YEAR BUILT'!N27</f>
         <v/>
       </c>
       <c r="K43" s="1" t="n"/>
@@ -8490,11 +8460,11 @@
         </is>
       </c>
       <c r="C44" s="50">
-        <f>'TOTAL RH'!G59</f>
+        <f>'YEAR BUILT'!G27</f>
         <v/>
       </c>
       <c r="D44" s="50">
-        <f>'TOTAL RH'!H59</f>
+        <f>'YEAR BUILT'!H27</f>
         <v/>
       </c>
       <c r="E44" s="1" t="n"/>
@@ -8506,11 +8476,11 @@
         </is>
       </c>
       <c r="I44" s="50">
-        <f>'TOTAL RH'!O59</f>
+        <f>'YEAR BUILT'!O27</f>
         <v/>
       </c>
       <c r="J44" s="50">
-        <f>'TOTAL RH'!P59</f>
+        <f>'YEAR BUILT'!P27</f>
         <v/>
       </c>
       <c r="K44" s="1" t="n"/>
@@ -8542,7 +8512,7 @@
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="55" t="inlineStr">
         <is>
-          <t>Full 2010-2026 Year x Brand x Size breakdown is on the TOTAL RH sheet.</t>
+          <t>Full 2010-2026 Year x Brand x Size breakdown is on the YEAR BUILT sheet.</t>
         </is>
       </c>
       <c r="C46" s="1" t="n"/>

--- a/Stock_Daily_Reefer_10-8.xlsx
+++ b/Stock_Daily_Reefer_10-8.xlsx
@@ -5231,22 +5231,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="23.57142857142857" customWidth="1" min="2" max="2"/>
+    <col width="8.714285714285714" customWidth="1" min="3" max="3"/>
+    <col width="8.714285714285714" customWidth="1" min="4" max="4"/>
+    <col width="8.714285714285714" customWidth="1" min="5" max="5"/>
+    <col width="8.714285714285714" customWidth="1" min="6" max="6"/>
+    <col width="8.714285714285714" customWidth="1" min="7" max="7"/>
+    <col width="23.57142857142857" customWidth="1" min="8" max="8"/>
+    <col width="8.714285714285714" customWidth="1" min="9" max="9"/>
+    <col width="8.714285714285714" customWidth="1" min="10" max="10"/>
+    <col width="8.714285714285714" customWidth="1" min="11" max="11"/>
+    <col width="8.714285714285714" customWidth="1" min="12" max="12"/>
+    <col width="8.714285714285714" customWidth="1" min="13" max="13"/>
+    <col width="8.714285714285714" customWidth="1" min="14" max="14"/>
+    <col width="8.714285714285714" customWidth="1" min="15" max="15"/>
+    <col width="8.714285714285714" customWidth="1" min="16" max="16"/>
+    <col width="8.714285714285714" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">
@@ -6396,22 +6396,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8.714285714285714" customWidth="1" min="2" max="2"/>
+    <col width="8.714285714285714" customWidth="1" min="3" max="3"/>
+    <col width="8.714285714285714" customWidth="1" min="4" max="4"/>
+    <col width="8.714285714285714" customWidth="1" min="5" max="5"/>
+    <col width="8.714285714285714" customWidth="1" min="6" max="6"/>
+    <col width="8.714285714285714" customWidth="1" min="7" max="7"/>
+    <col width="8.714285714285714" customWidth="1" min="8" max="8"/>
+    <col width="8.714285714285714" customWidth="1" min="9" max="9"/>
+    <col width="8.714285714285714" customWidth="1" min="10" max="10"/>
+    <col width="8.714285714285714" customWidth="1" min="11" max="11"/>
+    <col width="8.714285714285714" customWidth="1" min="12" max="12"/>
+    <col width="8.714285714285714" customWidth="1" min="13" max="13"/>
+    <col width="8.714285714285714" customWidth="1" min="14" max="14"/>
+    <col width="8.714285714285714" customWidth="1" min="15" max="15"/>
+    <col width="8.714285714285714" customWidth="1" min="16" max="16"/>
+    <col width="8.714285714285714" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">

--- a/Stock_Daily_Reefer_10-8.xlsx
+++ b/Stock_Daily_Reefer_10-8.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'TOTAL RH'!$A$1:$Q$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'YEAR BUILT'!$A$1:$Q$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'TOTAL RH'!$A$1:$Q$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'YEAR BUILT'!$A$1:$Q$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,10 +47,6 @@
       <i val="1"/>
     </font>
     <font>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
@@ -68,6 +64,10 @@
       <b val="1"/>
       <color rgb="00EB6834"/>
       <sz val="20"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
     <font/>
     <font>
@@ -144,17 +144,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00808080"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="002A78D6"/>
       <sz val="11"/>
@@ -172,6 +161,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
       <sz val="11"/>
     </font>
     <font>
@@ -255,7 +250,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -284,6 +279,14 @@
       <right style="thin">
         <color rgb="00BFBFBF"/>
       </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
       <top style="thin">
         <color rgb="00BFBFBF"/>
       </top>
@@ -416,13 +419,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -430,9 +434,15 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -440,19 +450,15 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -465,42 +471,42 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -510,27 +516,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -538,25 +544,25 @@
     <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5227,16 +5233,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="4.571428571428571" customWidth="1" min="1" max="1"/>
     <col width="23.57142857142857" customWidth="1" min="2" max="2"/>
     <col width="8.714285714285714" customWidth="1" min="3" max="3"/>
     <col width="8.714285714285714" customWidth="1" min="4" max="4"/>
     <col width="8.714285714285714" customWidth="1" min="5" max="5"/>
     <col width="8.714285714285714" customWidth="1" min="6" max="6"/>
-    <col width="8.714285714285714" customWidth="1" min="7" max="7"/>
+    <col width="4.571428571428571" customWidth="1" min="7" max="7"/>
     <col width="23.57142857142857" customWidth="1" min="8" max="8"/>
     <col width="8.714285714285714" customWidth="1" min="9" max="9"/>
     <col width="8.714285714285714" customWidth="1" min="10" max="10"/>
@@ -5249,21 +5255,21 @@
     <col width="8.714285714285714" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13" customHeight="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="3">
         <f>"Stock vs Booking Report - Reefer (20'RE / 40'RH)  as of "&amp;DAY(Control!$B$1)&amp;" "&amp;CHOOSE(MONTH(Control!$B$1),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;" "&amp;YEAR(Control!$B$1)</f>
         <v/>
       </c>
-      <c r="B1" s="56" t="n"/>
-      <c r="C1" s="56" t="n"/>
-      <c r="D1" s="56" t="n"/>
-      <c r="E1" s="56" t="n"/>
-      <c r="F1" s="56" t="n"/>
-      <c r="G1" s="56" t="n"/>
-      <c r="H1" s="56" t="n"/>
-      <c r="I1" s="56" t="n"/>
-      <c r="J1" s="56" t="n"/>
-      <c r="K1" s="57" t="n"/>
+      <c r="B1" s="57" t="n"/>
+      <c r="C1" s="57" t="n"/>
+      <c r="D1" s="57" t="n"/>
+      <c r="E1" s="57" t="n"/>
+      <c r="F1" s="57" t="n"/>
+      <c r="G1" s="57" t="n"/>
+      <c r="H1" s="57" t="n"/>
+      <c r="I1" s="57" t="n"/>
+      <c r="J1" s="57" t="n"/>
+      <c r="K1" s="58" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="n"/>
@@ -5271,684 +5277,620 @@
     </row>
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>BKK27 / BC2</t>
-        </is>
-      </c>
-      <c r="C2" s="56" t="n"/>
-      <c r="D2" s="57" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
       <c r="E2" s="1" t="n"/>
       <c r="F2" s="1" t="n"/>
       <c r="G2" s="1" t="n"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>LCH27 / HAST</t>
-        </is>
-      </c>
-      <c r="I2" s="56" t="n"/>
-      <c r="J2" s="57" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>STOCK</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>22RE</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>WK</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>BKK27 / BC2</t>
+        </is>
+      </c>
+      <c r="C3" s="57" t="n"/>
+      <c r="D3" s="58" t="n"/>
       <c r="E3" s="1" t="n"/>
       <c r="F3" s="1" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>WK</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>LCH27 / HAST</t>
+        </is>
+      </c>
+      <c r="I3" s="57" t="n"/>
+      <c r="J3" s="58" t="n"/>
       <c r="K3" s="1" t="n"/>
       <c r="L3" s="1" t="n"/>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="N3" s="8">
-        <f>C4</f>
-        <v/>
-      </c>
-      <c r="O3" s="8">
-        <f>D4</f>
-        <v/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>STOCK</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>22RE</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Stock empty in yard</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>38</v>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>WK</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
       </c>
       <c r="E4" s="1" t="n"/>
       <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>Stock empty in yard</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>53</v>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>WK</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
       </c>
       <c r="K4" s="1" t="n"/>
       <c r="L4" s="1" t="n"/>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>HAST</t>
-        </is>
-      </c>
-      <c r="N4" s="8">
-        <f>I4</f>
-        <v/>
-      </c>
-      <c r="O4" s="8">
-        <f>J4</f>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="N4" s="10">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="O4" s="10">
+        <f>D5</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="7">
-        <f>Control!$A$4</f>
-        <v/>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Booking Pending pick up</t>
-        </is>
-      </c>
-      <c r="C5" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&lt;"&amp;Control!$B$1)</f>
-        <v/>
-      </c>
-      <c r="D5" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&lt;"&amp;Control!$B$1)</f>
-        <v/>
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Stock empty in yard</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="n"/>
       <c r="F5" s="1" t="n"/>
-      <c r="G5" s="7">
-        <f>Control!$A$4</f>
-        <v/>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Booking Pending pick up</t>
-        </is>
-      </c>
-      <c r="I5" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&lt;"&amp;Control!$B$1)</f>
-        <v/>
-      </c>
-      <c r="J5" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&lt;"&amp;Control!$B$1)</f>
-        <v/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Stock empty in yard</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>53</v>
       </c>
       <c r="K5" s="1" t="n"/>
       <c r="L5" s="1" t="n"/>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="N5" s="6">
-        <f>SUM(N3:N4)</f>
-        <v/>
-      </c>
-      <c r="O5" s="6">
-        <f>SUM(O3:O4)</f>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>HAST</t>
+        </is>
+      </c>
+      <c r="N5" s="10">
+        <f>I5</f>
+        <v/>
+      </c>
+      <c r="O5" s="10">
+        <f>J5</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="7">
+      <c r="A6" s="14">
         <f>Control!$A$4</f>
         <v/>
       </c>
-      <c r="B6" s="7">
-        <f>"Booking on "&amp;DAY(Control!$B$1)&amp;" "&amp;CHOOSE(MONTH(Control!$B$1),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
-        <v/>
-      </c>
-      <c r="C6" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"="&amp;Control!$B$1)</f>
-        <v/>
-      </c>
-      <c r="D6" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"="&amp;Control!$B$1)</f>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Booking Pending pick up</t>
+        </is>
+      </c>
+      <c r="C6" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&lt;"&amp;Control!$B$1)</f>
+        <v/>
+      </c>
+      <c r="D6" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&lt;"&amp;Control!$B$1)</f>
         <v/>
       </c>
       <c r="E6" s="1" t="n"/>
       <c r="F6" s="1" t="n"/>
-      <c r="G6" s="7">
+      <c r="G6" s="14">
         <f>Control!$A$4</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>"Booking on "&amp;DAY(Control!$B$1)&amp;" "&amp;CHOOSE(MONTH(Control!$B$1),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
-        <v/>
-      </c>
-      <c r="I6" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"="&amp;Control!$B$1)</f>
-        <v/>
-      </c>
-      <c r="J6" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"="&amp;Control!$B$1)</f>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Booking Pending pick up</t>
+        </is>
+      </c>
+      <c r="I6" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&lt;"&amp;Control!$B$1)</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&lt;"&amp;Control!$B$1)</f>
         <v/>
       </c>
       <c r="K6" s="1" t="n"/>
       <c r="L6" s="1" t="n"/>
-      <c r="M6" s="1" t="n"/>
-      <c r="N6" s="1" t="n"/>
-      <c r="O6" s="1" t="n"/>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="N6" s="7">
+        <f>SUM(N4:N5)</f>
+        <v/>
+      </c>
+      <c r="O6" s="7">
+        <f>SUM(O4:O5)</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="7">
+      <c r="A7" s="14">
         <f>Control!$A$4</f>
         <v/>
       </c>
-      <c r="B7" s="7">
-        <f>"Booking on "&amp;IF(Control!$B$9=Control!$C$4,DAY(Control!$B$9)&amp;" "&amp;CHOOSE(MONTH(Control!$B$9),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B$9)=MONTH(Control!$C$4),DAY(Control!$B$9)&amp;"-"&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B$9)&amp;" "&amp;CHOOSE(MONTH(Control!$B$9),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
-        <v/>
-      </c>
-      <c r="C7" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B$9,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C$4)</f>
-        <v/>
-      </c>
-      <c r="D7" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B$9,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C$4)</f>
+      <c r="B7" s="9">
+        <f>"Booking on "&amp;DAY(Control!$B$1)&amp;" "&amp;CHOOSE(MONTH(Control!$B$1),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
+        <v/>
+      </c>
+      <c r="C7" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"="&amp;Control!$B$1)</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"="&amp;Control!$B$1)</f>
         <v/>
       </c>
       <c r="E7" s="1" t="n"/>
       <c r="F7" s="1" t="n"/>
-      <c r="G7" s="7">
+      <c r="G7" s="14">
         <f>Control!$A$4</f>
         <v/>
       </c>
-      <c r="H7" s="7">
-        <f>"Booking on "&amp;IF(Control!$B$9=Control!$C$4,DAY(Control!$B$9)&amp;" "&amp;CHOOSE(MONTH(Control!$B$9),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B$9)=MONTH(Control!$C$4),DAY(Control!$B$9)&amp;"-"&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B$9)&amp;" "&amp;CHOOSE(MONTH(Control!$B$9),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
-        <v/>
-      </c>
-      <c r="I7" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B$9,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J7" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B$9,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C$4)</f>
+      <c r="H7" s="9">
+        <f>"Booking on "&amp;DAY(Control!$B$1)&amp;" "&amp;CHOOSE(MONTH(Control!$B$1),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
+        <v/>
+      </c>
+      <c r="I7" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"="&amp;Control!$B$1)</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"="&amp;Control!$B$1)</f>
         <v/>
       </c>
       <c r="K7" s="1" t="n"/>
       <c r="L7" s="1" t="n"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>BOOKING</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>22RE</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
+      <c r="M7" s="1" t="n"/>
+      <c r="N7" s="1" t="n"/>
+      <c r="O7" s="1" t="n"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="12">
-        <f>"AV Balance till "&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
-        <v/>
-      </c>
-      <c r="C8" s="58">
-        <f>C4-C5-C6-C7</f>
-        <v/>
-      </c>
-      <c r="D8" s="58">
-        <f>D4-D5-D6-D7</f>
+      <c r="A8" s="14">
+        <f>Control!$A$4</f>
+        <v/>
+      </c>
+      <c r="B8" s="9">
+        <f>"Booking on "&amp;IF(Control!$B$9=Control!$C$4,DAY(Control!$B$9)&amp;" "&amp;CHOOSE(MONTH(Control!$B$9),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B$9)=MONTH(Control!$C$4),DAY(Control!$B$9)&amp;"-"&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B$9)&amp;" "&amp;CHOOSE(MONTH(Control!$B$9),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
+        <v/>
+      </c>
+      <c r="C8" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B$9,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C$4)</f>
+        <v/>
+      </c>
+      <c r="D8" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B$9,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C$4)</f>
         <v/>
       </c>
       <c r="E8" s="1" t="n"/>
       <c r="F8" s="1" t="n"/>
-      <c r="G8" s="1" t="n"/>
-      <c r="H8" s="12">
-        <f>"AV Balance till "&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
-        <v/>
-      </c>
-      <c r="I8" s="58">
-        <f>I4-I5-I6-I7</f>
-        <v/>
-      </c>
-      <c r="J8" s="58">
-        <f>J4-J5-J6-J7</f>
+      <c r="G8" s="14">
+        <f>Control!$A$4</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>"Booking on "&amp;IF(Control!$B$9=Control!$C$4,DAY(Control!$B$9)&amp;" "&amp;CHOOSE(MONTH(Control!$B$9),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B$9)=MONTH(Control!$C$4),DAY(Control!$B$9)&amp;"-"&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B$9)&amp;" "&amp;CHOOSE(MONTH(Control!$B$9),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
+        <v/>
+      </c>
+      <c r="I8" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B$9,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C$4)</f>
+        <v/>
+      </c>
+      <c r="J8" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B$9,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C$4)</f>
         <v/>
       </c>
       <c r="K8" s="1" t="n"/>
       <c r="L8" s="1" t="n"/>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="N8" s="8">
-        <f>C5+C6+C7+C9+C11</f>
-        <v/>
-      </c>
-      <c r="O8" s="8">
-        <f>D5+D6+D7+D9+D11</f>
-        <v/>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>BOOKING</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>22RE</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="7">
-        <f>Control!$A$5</f>
-        <v/>
-      </c>
-      <c r="B9" s="7">
-        <f>"Booking on "&amp;IF(Control!$B5=Control!$C5,DAY(Control!$B5)&amp;" "&amp;CHOOSE(MONTH(Control!$B5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B5)=MONTH(Control!$C5),DAY(Control!$B5)&amp;"-"&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B5)&amp;" "&amp;CHOOSE(MONTH(Control!$B5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
-        <v/>
-      </c>
-      <c r="C9" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B5,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C5)</f>
-        <v/>
-      </c>
-      <c r="D9" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B5,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C5)</f>
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="16">
+        <f>"AV Balance till "&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
+        <v/>
+      </c>
+      <c r="C9" s="59">
+        <f>C5-C6-C7-C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="59">
+        <f>D5-D6-D7-D8</f>
         <v/>
       </c>
       <c r="E9" s="1" t="n"/>
       <c r="F9" s="1" t="n"/>
-      <c r="G9" s="7">
-        <f>Control!$A$5</f>
-        <v/>
-      </c>
-      <c r="H9" s="7">
-        <f>"Booking on "&amp;IF(Control!$B5=Control!$C5,DAY(Control!$B5)&amp;" "&amp;CHOOSE(MONTH(Control!$B5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B5)=MONTH(Control!$C5),DAY(Control!$B5)&amp;"-"&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B5)&amp;" "&amp;CHOOSE(MONTH(Control!$B5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
-        <v/>
-      </c>
-      <c r="I9" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B5,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C5)</f>
-        <v/>
-      </c>
-      <c r="J9" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B5,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C5)</f>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="16">
+        <f>"AV Balance till "&amp;DAY(Control!$C$4)&amp;" "&amp;CHOOSE(MONTH(Control!$C$4),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
+        <v/>
+      </c>
+      <c r="I9" s="59">
+        <f>I5-I6-I7-I8</f>
+        <v/>
+      </c>
+      <c r="J9" s="59">
+        <f>J5-J6-J7-J8</f>
         <v/>
       </c>
       <c r="K9" s="1" t="n"/>
       <c r="L9" s="1" t="n"/>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>HAST</t>
-        </is>
-      </c>
-      <c r="N9" s="8">
-        <f>I5+I6+I7+I9+I11</f>
-        <v/>
-      </c>
-      <c r="O9" s="8">
-        <f>J5+J6+J7+J9+J11</f>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="N9" s="10">
+        <f>C6+C7+C8+C11+C14</f>
+        <v/>
+      </c>
+      <c r="O9" s="10">
+        <f>D6+D7+D8+D11+D14</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="12">
-        <f>"AV Balance till "&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
-        <v/>
-      </c>
-      <c r="C10" s="58">
-        <f>C8-C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="58">
-        <f>D8-D9</f>
-        <v/>
-      </c>
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
       <c r="E10" s="1" t="n"/>
       <c r="F10" s="1" t="n"/>
-      <c r="G10" s="1" t="n"/>
-      <c r="H10" s="12">
-        <f>"AV Balance till "&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
-        <v/>
-      </c>
-      <c r="I10" s="58">
-        <f>I8-I9</f>
-        <v/>
-      </c>
-      <c r="J10" s="59">
-        <f>J8-J9</f>
-        <v/>
-      </c>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
       <c r="K10" s="1" t="n"/>
       <c r="L10" s="1" t="n"/>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="N10" s="6">
-        <f>SUM(N8:N9)</f>
-        <v/>
-      </c>
-      <c r="O10" s="6">
-        <f>SUM(O8:O9)</f>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>HAST</t>
+        </is>
+      </c>
+      <c r="N10" s="10">
+        <f>I6+I7+I8+I11+I14</f>
+        <v/>
+      </c>
+      <c r="O10" s="10">
+        <f>J6+J7+J8+J11+J14</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="7">
-        <f>Control!$A$6</f>
-        <v/>
-      </c>
-      <c r="B11" s="7">
-        <f>"Booking on "&amp;IF(Control!$B6=Control!$C6,DAY(Control!$B6)&amp;" "&amp;CHOOSE(MONTH(Control!$B6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B6)=MONTH(Control!$C6),DAY(Control!$B6)&amp;"-"&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B6)&amp;" "&amp;CHOOSE(MONTH(Control!$B6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
-        <v/>
-      </c>
-      <c r="C11" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B6,BookingRaw!$B$2:$B$8000,"&lt;="&amp;DATE(2026,10,24))</f>
-        <v/>
-      </c>
-      <c r="D11" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B6,BookingRaw!$B$2:$B$8000,"&lt;="&amp;DATE(2026,10,24))</f>
+      <c r="A11" s="14">
+        <f>Control!$A$5</f>
+        <v/>
+      </c>
+      <c r="B11" s="9">
+        <f>"Booking on "&amp;IF(Control!$B5=Control!$C5,DAY(Control!$B5)&amp;" "&amp;CHOOSE(MONTH(Control!$B5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B5)=MONTH(Control!$C5),DAY(Control!$B5)&amp;"-"&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B5)&amp;" "&amp;CHOOSE(MONTH(Control!$B5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
+        <v/>
+      </c>
+      <c r="C11" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B5,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C5)</f>
+        <v/>
+      </c>
+      <c r="D11" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B5,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C5)</f>
         <v/>
       </c>
       <c r="E11" s="1" t="n"/>
       <c r="F11" s="1" t="n"/>
-      <c r="G11" s="7">
-        <f>Control!$A$6</f>
-        <v/>
-      </c>
-      <c r="H11" s="7">
-        <f>"Booking on "&amp;IF(Control!$B6=Control!$C6,DAY(Control!$B6)&amp;" "&amp;CHOOSE(MONTH(Control!$B6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B6)=MONTH(Control!$C6),DAY(Control!$B6)&amp;"-"&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B6)&amp;" "&amp;CHOOSE(MONTH(Control!$B6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
-        <v/>
-      </c>
-      <c r="I11" s="7">
-        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B6,BookingRaw!$B$2:$B$8000,"&lt;="&amp;DATE(2026,10,24))</f>
-        <v/>
-      </c>
-      <c r="J11" s="7">
-        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B6,BookingRaw!$B$2:$B$8000,"&lt;="&amp;DATE(2026,10,24))</f>
+      <c r="G11" s="14">
+        <f>Control!$A$5</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>"Booking on "&amp;IF(Control!$B5=Control!$C5,DAY(Control!$B5)&amp;" "&amp;CHOOSE(MONTH(Control!$B5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B5)=MONTH(Control!$C5),DAY(Control!$B5)&amp;"-"&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B5)&amp;" "&amp;CHOOSE(MONTH(Control!$B5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
+        <v/>
+      </c>
+      <c r="I11" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B5,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C5)</f>
+        <v/>
+      </c>
+      <c r="J11" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B5,BookingRaw!$B$2:$B$8000,"&lt;="&amp;Control!$C5)</f>
         <v/>
       </c>
       <c r="K11" s="1" t="n"/>
       <c r="L11" s="1" t="n"/>
-      <c r="M11" s="1" t="n"/>
-      <c r="N11" s="1" t="n"/>
-      <c r="O11" s="1" t="n"/>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="N11" s="7">
+        <f>SUM(N9:N10)</f>
+        <v/>
+      </c>
+      <c r="O11" s="7">
+        <f>SUM(O9:O10)</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="12">
-        <f>"AV Balance till "&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
-        <v/>
-      </c>
-      <c r="C12" s="58">
-        <f>C10-C11</f>
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="16">
+        <f>"AV Balance till "&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
+        <v/>
+      </c>
+      <c r="C12" s="59">
+        <f>C9-C11</f>
         <v/>
       </c>
       <c r="D12" s="59">
-        <f>D10-D11</f>
+        <f>D9-D11</f>
         <v/>
       </c>
       <c r="E12" s="1" t="n"/>
       <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="12">
-        <f>"AV Balance till "&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
-        <v/>
-      </c>
-      <c r="I12" s="58">
-        <f>I10-I11</f>
-        <v/>
-      </c>
-      <c r="J12" s="59">
-        <f>J10-J11</f>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="16">
+        <f>"AV Balance till "&amp;DAY(Control!$C5)&amp;" "&amp;CHOOSE(MONTH(Control!$C5),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
+        <v/>
+      </c>
+      <c r="I12" s="59">
+        <f>I9-I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="60">
+        <f>J9-J11</f>
         <v/>
       </c>
       <c r="K12" s="1" t="n"/>
       <c r="L12" s="1" t="n"/>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>BALANCE</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>22RE</t>
-        </is>
-      </c>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
+      <c r="M12" s="1" t="n"/>
+      <c r="N12" s="1" t="n"/>
+      <c r="O12" s="1" t="n"/>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
       <c r="E13" s="1" t="n"/>
       <c r="F13" s="1" t="n"/>
-      <c r="G13" s="1" t="n"/>
-      <c r="H13" s="1" t="n"/>
-      <c r="I13" s="1" t="n"/>
-      <c r="J13" s="1" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
       <c r="K13" s="1" t="n"/>
       <c r="L13" s="1" t="n"/>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="N13" s="8">
-        <f>C12</f>
-        <v/>
-      </c>
-      <c r="O13" s="8">
-        <f>D12</f>
-        <v/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>BALANCE</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>22RE</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Remarks:</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>AV = stock with move code IED / IEP / IER (available)   |   DMG = move code OER (damaged)</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="1" t="n"/>
+      <c r="A14" s="14">
+        <f>Control!$A$6</f>
+        <v/>
+      </c>
+      <c r="B14" s="9">
+        <f>"Booking on "&amp;IF(Control!$B6=Control!$C6,DAY(Control!$B6)&amp;" "&amp;CHOOSE(MONTH(Control!$B6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B6)=MONTH(Control!$C6),DAY(Control!$B6)&amp;"-"&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B6)&amp;" "&amp;CHOOSE(MONTH(Control!$B6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
+        <v/>
+      </c>
+      <c r="C14" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B6,BookingRaw!$B$2:$B$8000,"&lt;="&amp;DATE(2026,10,24))</f>
+        <v/>
+      </c>
+      <c r="D14" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"BKK27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B6,BookingRaw!$B$2:$B$8000,"&lt;="&amp;DATE(2026,10,24))</f>
+        <v/>
+      </c>
       <c r="E14" s="1" t="n"/>
       <c r="F14" s="1" t="n"/>
-      <c r="G14" s="1" t="n"/>
-      <c r="H14" s="1" t="n"/>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="n"/>
+      <c r="G14" s="14">
+        <f>Control!$A$6</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>"Booking on "&amp;IF(Control!$B6=Control!$C6,DAY(Control!$B6)&amp;" "&amp;CHOOSE(MONTH(Control!$B6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),IF(MONTH(Control!$B6)=MONTH(Control!$C6),DAY(Control!$B6)&amp;"-"&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC"),DAY(Control!$B6)&amp;" "&amp;CHOOSE(MONTH(Control!$B6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")&amp;"-"&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")))</f>
+        <v/>
+      </c>
+      <c r="I14" s="9">
+        <f>SUMIFS(BookingRaw!$C$2:$C$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B6,BookingRaw!$B$2:$B$8000,"&lt;="&amp;DATE(2026,10,24))</f>
+        <v/>
+      </c>
+      <c r="J14" s="9">
+        <f>SUMIFS(BookingRaw!$D$2:$D$8000,BookingRaw!$A$2:$A$8000,"LCH27",BookingRaw!$B$2:$B$8000,"&gt;="&amp;Control!$B6,BookingRaw!$B$2:$B$8000,"&lt;="&amp;DATE(2026,10,24))</f>
+        <v/>
+      </c>
       <c r="K14" s="1" t="n"/>
       <c r="L14" s="1" t="n"/>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>HAST</t>
-        </is>
-      </c>
-      <c r="N14" s="8">
-        <f>I12</f>
-        <v/>
-      </c>
-      <c r="O14" s="8">
-        <f>J12</f>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="N14" s="10">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="O14" s="10">
+        <f>D15</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="16">
+        <f>"AV Balance till "&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
+        <v/>
+      </c>
+      <c r="C15" s="59">
+        <f>C12-C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="60">
+        <f>D12-D14</f>
+        <v/>
       </c>
       <c r="E15" s="1" t="n"/>
       <c r="F15" s="1" t="n"/>
-      <c r="G15" s="1" t="n"/>
-      <c r="H15" s="1" t="n"/>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="16">
+        <f>"AV Balance till "&amp;DAY(Control!$C6)&amp;" "&amp;CHOOSE(MONTH(Control!$C6),"JAN","FEB","MAR","APR","MAY","JUN","JUL","AUG","SEP","OCT","NOV","DEC")</f>
+        <v/>
+      </c>
+      <c r="I15" s="59">
+        <f>I12-I14</f>
+        <v/>
+      </c>
+      <c r="J15" s="60">
+        <f>J12-J14</f>
+        <v/>
       </c>
       <c r="K15" s="1" t="n"/>
       <c r="L15" s="1" t="n"/>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="N15" s="6">
-        <f>SUM(N13:N14)</f>
-        <v/>
-      </c>
-      <c r="O15" s="6">
-        <f>SUM(O13:O14)</f>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>HAST</t>
+        </is>
+      </c>
+      <c r="N15" s="10">
+        <f>I15</f>
+        <v/>
+      </c>
+      <c r="O15" s="10">
+        <f>J15</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>AV</t>
-        </is>
-      </c>
-      <c r="C16" s="8">
-        <f>COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IED")+COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IEP")+COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IER")</f>
-        <v/>
-      </c>
-      <c r="D16" s="8">
-        <f>COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IED")+COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IEP")+COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IER")</f>
-        <v/>
-      </c>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
       <c r="E16" s="1" t="n"/>
       <c r="F16" s="1" t="n"/>
       <c r="G16" s="1" t="n"/>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>AV</t>
-        </is>
-      </c>
-      <c r="I16" s="8">
-        <f>COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IED")+COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IEP")+COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IER")</f>
-        <v/>
-      </c>
-      <c r="J16" s="8">
-        <f>COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IED")+COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IEP")+COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IER")</f>
-        <v/>
-      </c>
+      <c r="H16" s="1" t="n"/>
+      <c r="I16" s="1" t="n"/>
+      <c r="J16" s="1" t="n"/>
       <c r="K16" s="1" t="n"/>
       <c r="L16" s="1" t="n"/>
-      <c r="M16" s="1" t="n"/>
-      <c r="N16" s="1" t="n"/>
-      <c r="O16" s="1" t="n"/>
+      <c r="M16" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="N16" s="7">
+        <f>SUM(N14:N15)</f>
+        <v/>
+      </c>
+      <c r="O16" s="7">
+        <f>SUM(O14:O15)</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>DMG</t>
-        </is>
-      </c>
-      <c r="C17" s="8">
-        <f>COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"OER")</f>
-        <v/>
-      </c>
-      <c r="D17" s="8">
-        <f>COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"OER")</f>
-        <v/>
-      </c>
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
+      <c r="D17" s="1" t="n"/>
       <c r="E17" s="1" t="n"/>
       <c r="F17" s="1" t="n"/>
       <c r="G17" s="1" t="n"/>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>DMG</t>
-        </is>
-      </c>
-      <c r="I17" s="8">
-        <f>COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"OER")</f>
-        <v/>
-      </c>
-      <c r="J17" s="8">
-        <f>COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"OER")</f>
-        <v/>
-      </c>
+      <c r="H17" s="1" t="n"/>
+      <c r="I17" s="1" t="n"/>
+      <c r="J17" s="1" t="n"/>
       <c r="K17" s="1" t="n"/>
       <c r="L17" s="1" t="n"/>
       <c r="M17" s="1" t="n"/>
@@ -5957,15 +5899,39 @@
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>BKK27 / BC2</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
       <c r="E18" s="1" t="n"/>
       <c r="F18" s="1" t="n"/>
       <c r="G18" s="1" t="n"/>
-      <c r="H18" s="1" t="n"/>
-      <c r="I18" s="1" t="n"/>
-      <c r="J18" s="1" t="n"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>LCH27 / HAST</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
       <c r="K18" s="1" t="n"/>
       <c r="L18" s="1" t="n"/>
       <c r="M18" s="1" t="n"/>
@@ -5974,15 +5940,35 @@
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="n"/>
-      <c r="C19" s="1" t="n"/>
-      <c r="D19" s="1" t="n"/>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="C19" s="10">
+        <f>COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IED")+COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IEP")+COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IER")</f>
+        <v/>
+      </c>
+      <c r="D19" s="10">
+        <f>COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IED")+COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IEP")+COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IER")</f>
+        <v/>
+      </c>
       <c r="E19" s="1" t="n"/>
       <c r="F19" s="1" t="n"/>
       <c r="G19" s="1" t="n"/>
-      <c r="H19" s="1" t="n"/>
-      <c r="I19" s="1" t="n"/>
-      <c r="J19" s="1" t="n"/>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="I19" s="10">
+        <f>COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IED")+COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IEP")+COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"IER")</f>
+        <v/>
+      </c>
+      <c r="J19" s="10">
+        <f>COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IED")+COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IEP")+COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"IER")</f>
+        <v/>
+      </c>
       <c r="K19" s="1" t="n"/>
       <c r="L19" s="1" t="n"/>
       <c r="M19" s="1" t="n"/>
@@ -5991,24 +5977,36 @@
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>BKK / BC2 (BKK27)</t>
-        </is>
-      </c>
-      <c r="C20" s="56" t="n"/>
-      <c r="D20" s="56" t="n"/>
-      <c r="E20" s="57" t="n"/>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>DMG</t>
+        </is>
+      </c>
+      <c r="C20" s="10">
+        <f>COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"OER")</f>
+        <v/>
+      </c>
+      <c r="D20" s="10">
+        <f>COUNTIFS(StockRaw!$A$2:$A$132,"BKK27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"OER")</f>
+        <v/>
+      </c>
+      <c r="E20" s="1" t="n"/>
       <c r="F20" s="1" t="n"/>
       <c r="G20" s="1" t="n"/>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>LCH / HAST (LCH27)</t>
-        </is>
-      </c>
-      <c r="I20" s="56" t="n"/>
-      <c r="J20" s="56" t="n"/>
-      <c r="K20" s="57" t="n"/>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>DMG</t>
+        </is>
+      </c>
+      <c r="I20" s="10">
+        <f>COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"22RE",StockRaw!$C$2:$C$132,"OER")</f>
+        <v/>
+      </c>
+      <c r="J20" s="10">
+        <f>COUNTIFS(StockRaw!$A$2:$A$132,"LCH27",StockRaw!$B$2:$B$132,"45RE",StockRaw!$C$2:$C$132,"OER")</f>
+        <v/>
+      </c>
+      <c r="K20" s="1" t="n"/>
       <c r="L20" s="1" t="n"/>
       <c r="M20" s="1" t="n"/>
       <c r="N20" s="1" t="n"/>
@@ -6016,50 +6014,16 @@
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>YEAR BUILT 5 YEARS
-FOR DURIAN SEASON</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>CARRIER</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>DAIKIN</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>THERMO KING</t>
-        </is>
-      </c>
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="1" t="n"/>
+      <c r="D21" s="1" t="n"/>
+      <c r="E21" s="1" t="n"/>
       <c r="F21" s="1" t="n"/>
       <c r="G21" s="1" t="n"/>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>YEAR BUILT 5 YEARS
-FOR DURIAN SEASON</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>CARRIER</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>DAIKIN</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>THERMO KING</t>
-        </is>
-      </c>
+      <c r="H21" s="1" t="n"/>
+      <c r="I21" s="1" t="n"/>
+      <c r="J21" s="1" t="n"/>
+      <c r="K21" s="1" t="n"/>
       <c r="L21" s="1" t="n"/>
       <c r="M21" s="1" t="n"/>
       <c r="N21" s="1" t="n"/>
@@ -6067,40 +6031,16 @@
     </row>
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="60" t="n"/>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1" t="n"/>
       <c r="F22" s="1" t="n"/>
       <c r="G22" s="1" t="n"/>
-      <c r="H22" s="60" t="n"/>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>45RE</t>
-        </is>
-      </c>
+      <c r="H22" s="1" t="n"/>
+      <c r="I22" s="1" t="n"/>
+      <c r="J22" s="1" t="n"/>
+      <c r="K22" s="1" t="n"/>
       <c r="L22" s="1" t="n"/>
       <c r="M22" s="1" t="n"/>
       <c r="N22" s="1" t="n"/>
@@ -6108,32 +6048,24 @@
     </row>
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="8" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>BKK / BC2 (BKK27)</t>
+        </is>
+      </c>
+      <c r="C23" s="57" t="n"/>
+      <c r="D23" s="57" t="n"/>
+      <c r="E23" s="58" t="n"/>
       <c r="F23" s="1" t="n"/>
       <c r="G23" s="1" t="n"/>
-      <c r="H23" s="8" t="n">
-        <v>2026</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>LCH / HAST (LCH27)</t>
+        </is>
+      </c>
+      <c r="I23" s="57" t="n"/>
+      <c r="J23" s="57" t="n"/>
+      <c r="K23" s="58" t="n"/>
       <c r="L23" s="1" t="n"/>
       <c r="M23" s="1" t="n"/>
       <c r="N23" s="1" t="n"/>
@@ -6141,31 +6073,49 @@
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="8" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>1</v>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>YEAR BUILT 5 YEARS
+FOR DURIAN SEASON</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>CARRIER</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>DAIKIN</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>THERMO KING</t>
+        </is>
       </c>
       <c r="F24" s="1" t="n"/>
       <c r="G24" s="1" t="n"/>
-      <c r="H24" s="8" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="8" t="n">
-        <v>0</v>
+      <c r="H24" s="19" t="inlineStr">
+        <is>
+          <t>YEAR BUILT 5 YEARS
+FOR DURIAN SEASON</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>CARRIER</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>DAIKIN</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>THERMO KING</t>
+        </is>
       </c>
       <c r="L24" s="1" t="n"/>
       <c r="M24" s="1" t="n"/>
@@ -6174,31 +6124,39 @@
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0</v>
+      <c r="B25" s="61" t="n"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
       </c>
       <c r="F25" s="1" t="n"/>
       <c r="G25" s="1" t="n"/>
-      <c r="H25" s="8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>0</v>
+      <c r="H25" s="61" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>45RE</t>
+        </is>
       </c>
       <c r="L25" s="1" t="n"/>
       <c r="M25" s="1" t="n"/>
@@ -6207,30 +6165,30 @@
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="8" t="n">
+      <c r="B26" s="10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="1" t="n"/>
       <c r="G26" s="1" t="n"/>
-      <c r="H26" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="8" t="n">
+      <c r="H26" s="10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="1" t="n"/>
@@ -6240,30 +6198,30 @@
     </row>
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="8" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0</v>
+      <c r="B27" s="10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="F27" s="1" t="n"/>
       <c r="G27" s="1" t="n"/>
-      <c r="H27" s="8" t="n">
-        <v>2022</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="8" t="n">
+      <c r="H27" s="10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="1" t="n"/>
@@ -6273,30 +6231,30 @@
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="8" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="8" t="n">
+      <c r="B28" s="10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="1" t="n"/>
       <c r="G28" s="1" t="n"/>
-      <c r="H28" s="8" t="n">
-        <v>2021</v>
-      </c>
-      <c r="I28" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="8" t="n">
+      <c r="H28" s="10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="1" t="n"/>
@@ -6306,34 +6264,30 @@
     </row>
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>1</v>
+      <c r="B29" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="1" t="n"/>
       <c r="G29" s="1" t="n"/>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="6" t="n">
+      <c r="H29" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="1" t="n"/>
@@ -6343,42 +6297,145 @@
     </row>
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="n"/>
-      <c r="C30" s="1" t="n"/>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>OVER 5 Y</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="n">
-        <v>27</v>
+      <c r="B30" s="10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="1" t="n"/>
       <c r="G30" s="1" t="n"/>
-      <c r="H30" s="1" t="n"/>
-      <c r="I30" s="1" t="n"/>
-      <c r="J30" s="19" t="inlineStr">
-        <is>
-          <t>OVER 5 Y</t>
-        </is>
-      </c>
-      <c r="K30" s="20" t="n">
-        <v>40</v>
+      <c r="H30" s="10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="L30" s="1" t="n"/>
       <c r="M30" s="1" t="n"/>
       <c r="N30" s="1" t="n"/>
       <c r="O30" s="1" t="n"/>
     </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="10" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="n"/>
+      <c r="G31" s="1" t="n"/>
+      <c r="H31" s="10" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1" t="n"/>
+      <c r="M31" s="1" t="n"/>
+      <c r="N31" s="1" t="n"/>
+      <c r="O31" s="1" t="n"/>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1" t="n"/>
+      <c r="G32" s="1" t="n"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1" t="n"/>
+      <c r="M32" s="1" t="n"/>
+      <c r="N32" s="1" t="n"/>
+      <c r="O32" s="1" t="n"/>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="1" t="n"/>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>OVER 5 Y</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="F33" s="1" t="n"/>
+      <c r="G33" s="1" t="n"/>
+      <c r="H33" s="1" t="n"/>
+      <c r="I33" s="1" t="n"/>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>OVER 5 Y</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="L33" s="1" t="n"/>
+      <c r="M33" s="1" t="n"/>
+      <c r="N33" s="1" t="n"/>
+      <c r="O33" s="1" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="H3:J3"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H23:K23"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -6392,10 +6449,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="3.571428571428572" customWidth="1" min="1" max="1"/>
     <col width="8.714285714285714" customWidth="1" min="2" max="2"/>
     <col width="8.714285714285714" customWidth="1" min="3" max="3"/>
     <col width="8.714285714285714" customWidth="1" min="4" max="4"/>
@@ -6403,7 +6460,7 @@
     <col width="8.714285714285714" customWidth="1" min="6" max="6"/>
     <col width="8.714285714285714" customWidth="1" min="7" max="7"/>
     <col width="8.714285714285714" customWidth="1" min="8" max="8"/>
-    <col width="8.714285714285714" customWidth="1" min="9" max="9"/>
+    <col width="3.571428571428572" customWidth="1" min="9" max="9"/>
     <col width="8.714285714285714" customWidth="1" min="10" max="10"/>
     <col width="8.714285714285714" customWidth="1" min="11" max="11"/>
     <col width="8.714285714285714" customWidth="1" min="12" max="12"/>
@@ -6416,7 +6473,7 @@
   <sheetData>
     <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>CARGO CLASSIFICATION  (40'RH stock by Built Year, per depot)</t>
         </is>
@@ -6438,119 +6495,119 @@
     </row>
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="22" t="inlineStr">
-        <is>
-          <t>BKK27 DURIAN  (2021-2026)</t>
-        </is>
-      </c>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
-      <c r="F2" s="22" t="inlineStr">
-        <is>
-          <t>BKK27 NON DURIAN  (≤ 2020)</t>
-        </is>
-      </c>
-      <c r="G2" s="23" t="n"/>
-      <c r="H2" s="23" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
       <c r="I2" s="1" t="n"/>
-      <c r="J2" s="22" t="inlineStr">
-        <is>
-          <t>LCH27 DURIAN  (2021-2026)</t>
-        </is>
-      </c>
-      <c r="K2" s="23" t="n"/>
-      <c r="L2" s="23" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="n"/>
-      <c r="N2" s="22" t="inlineStr">
-        <is>
-          <t>LCH27 NON DURIAN  (≤ 2020)</t>
-        </is>
-      </c>
-      <c r="O2" s="23" t="n"/>
-      <c r="P2" s="23" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
     </row>
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="1" t="n"/>
-      <c r="B3" s="24">
-        <f>SUM(D10:D15)+SUM(F10:F15)+SUM(H10:H15)</f>
-        <v/>
-      </c>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>BKK27 DURIAN  (2021-2026)</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="24" t="n"/>
       <c r="E3" s="1" t="n"/>
-      <c r="F3" s="24">
-        <f>SUM(D16:D26)+SUM(F16:F26)+SUM(H16:H26)</f>
-        <v/>
-      </c>
-      <c r="G3" s="23" t="n"/>
-      <c r="H3" s="23" t="n"/>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>BKK27 NON DURIAN  (≤ 2020)</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="n"/>
+      <c r="H3" s="24" t="n"/>
       <c r="I3" s="1" t="n"/>
-      <c r="J3" s="25">
-        <f>SUM(L10:L15)+SUM(N10:N15)+SUM(P10:P15)</f>
-        <v/>
-      </c>
-      <c r="K3" s="23" t="n"/>
-      <c r="L3" s="23" t="n"/>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t>LCH27 DURIAN  (2021-2026)</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="n"/>
+      <c r="L3" s="24" t="n"/>
       <c r="M3" s="1" t="n"/>
-      <c r="N3" s="25">
-        <f>SUM(L16:L26)+SUM(N16:N26)+SUM(P16:P26)</f>
-        <v/>
-      </c>
-      <c r="O3" s="23" t="n"/>
-      <c r="P3" s="23" t="n"/>
+      <c r="N3" s="23" t="inlineStr">
+        <is>
+          <t>LCH27 NON DURIAN  (≤ 2020)</t>
+        </is>
+      </c>
+      <c r="O3" s="24" t="n"/>
+      <c r="P3" s="24" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="n"/>
-      <c r="D4" s="23" t="n"/>
+      <c r="B4" s="25">
+        <f>SUM(D11:D16)+SUM(F11:F16)+SUM(H11:H16)</f>
+        <v/>
+      </c>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
       <c r="E4" s="1" t="n"/>
-      <c r="F4" s="26" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="G4" s="23" t="n"/>
-      <c r="H4" s="23" t="n"/>
+      <c r="F4" s="25">
+        <f>SUM(D17:D27)+SUM(F17:F27)+SUM(H17:H27)</f>
+        <v/>
+      </c>
+      <c r="G4" s="24" t="n"/>
+      <c r="H4" s="24" t="n"/>
       <c r="I4" s="1" t="n"/>
-      <c r="J4" s="26" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="K4" s="23" t="n"/>
-      <c r="L4" s="23" t="n"/>
+      <c r="J4" s="26">
+        <f>SUM(L11:L16)+SUM(N11:N16)+SUM(P11:P16)</f>
+        <v/>
+      </c>
+      <c r="K4" s="24" t="n"/>
+      <c r="L4" s="24" t="n"/>
       <c r="M4" s="1" t="n"/>
-      <c r="N4" s="26" t="inlineStr">
-        <is>
-          <t>40'RH stock</t>
-        </is>
-      </c>
-      <c r="O4" s="23" t="n"/>
-      <c r="P4" s="23" t="n"/>
+      <c r="N4" s="26">
+        <f>SUM(L17:L27)+SUM(N17:N27)+SUM(P17:P27)</f>
+        <v/>
+      </c>
+      <c r="O4" s="24" t="n"/>
+      <c r="P4" s="24" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
       <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="n"/>
+      <c r="H5" s="24" t="n"/>
       <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="n"/>
-      <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
+      <c r="J5" s="27" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="24" t="n"/>
       <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="n"/>
-      <c r="O5" s="1" t="n"/>
-      <c r="P5" s="1" t="n"/>
+      <c r="N5" s="27" t="inlineStr">
+        <is>
+          <t>40'RH stock</t>
+        </is>
+      </c>
+      <c r="O5" s="24" t="n"/>
+      <c r="P5" s="24" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="1" t="n"/>
@@ -6572,672 +6629,690 @@
     </row>
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+      <c r="H7" s="1" t="n"/>
+      <c r="I7" s="1" t="n"/>
+      <c r="J7" s="1" t="n"/>
+      <c r="K7" s="1" t="n"/>
+      <c r="L7" s="1" t="n"/>
+      <c r="M7" s="1" t="n"/>
+      <c r="N7" s="1" t="n"/>
+      <c r="O7" s="1" t="n"/>
+      <c r="P7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>BKK27 / BC2  —  Stock by Built Year x Brand x Size</t>
         </is>
       </c>
-      <c r="C7" s="56" t="n"/>
-      <c r="D7" s="56" t="n"/>
-      <c r="E7" s="56" t="n"/>
-      <c r="F7" s="56" t="n"/>
-      <c r="G7" s="56" t="n"/>
-      <c r="H7" s="57" t="n"/>
-      <c r="I7" s="1" t="n"/>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="C8" s="57" t="n"/>
+      <c r="D8" s="57" t="n"/>
+      <c r="E8" s="57" t="n"/>
+      <c r="F8" s="57" t="n"/>
+      <c r="G8" s="57" t="n"/>
+      <c r="H8" s="58" t="n"/>
+      <c r="I8" s="1" t="n"/>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LCH27 / HAST  —  Stock by Built Year x Brand x Size</t>
         </is>
       </c>
-      <c r="K7" s="56" t="n"/>
-      <c r="L7" s="56" t="n"/>
-      <c r="M7" s="56" t="n"/>
-      <c r="N7" s="56" t="n"/>
-      <c r="O7" s="56" t="n"/>
-      <c r="P7" s="57" t="n"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="K8" s="57" t="n"/>
+      <c r="L8" s="57" t="n"/>
+      <c r="M8" s="57" t="n"/>
+      <c r="N8" s="57" t="n"/>
+      <c r="O8" s="57" t="n"/>
+      <c r="P8" s="58" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>YEAR
 BUILT</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>CARRIER</t>
         </is>
       </c>
-      <c r="D8" s="57" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="D9" s="58" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>DAIKIN</t>
         </is>
       </c>
-      <c r="F8" s="57" t="n"/>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F9" s="58" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>THERMO KING</t>
         </is>
       </c>
-      <c r="H8" s="57" t="n"/>
-      <c r="I8" s="1" t="n"/>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="H9" s="58" t="n"/>
+      <c r="I9" s="1" t="n"/>
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>YEAR
 BUILT</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>CARRIER</t>
         </is>
       </c>
-      <c r="L8" s="57" t="n"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="L9" s="58" t="n"/>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>DAIKIN</t>
         </is>
       </c>
-      <c r="N8" s="57" t="n"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="N9" s="58" t="n"/>
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>THERMO KING</t>
         </is>
       </c>
-      <c r="P8" s="57" t="n"/>
-    </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="60" t="n"/>
-      <c r="C9" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="F9" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="H9" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="n"/>
-      <c r="J9" s="60" t="n"/>
-      <c r="K9" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="L9" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="M9" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="N9" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
-      <c r="O9" s="28" t="inlineStr">
-        <is>
-          <t>20'RE</t>
-        </is>
-      </c>
-      <c r="P9" s="28" t="inlineStr">
-        <is>
-          <t>40'RH</t>
-        </is>
-      </c>
+      <c r="P9" s="58" t="n"/>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C10" s="30" t="n"/>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
+      <c r="B10" s="61" t="n"/>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="F10" s="29" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
       <c r="I10" s="1" t="n"/>
-      <c r="J10" s="29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="K10" s="30" t="n"/>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="30" t="n"/>
-      <c r="N10" s="30" t="n"/>
-      <c r="O10" s="30" t="n"/>
-      <c r="P10" s="30" t="n"/>
+      <c r="J10" s="61" t="n"/>
+      <c r="K10" s="29" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="L10" s="29" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="M10" s="29" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="N10" s="29" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
+      <c r="O10" s="29" t="inlineStr">
+        <is>
+          <t>20'RE</t>
+        </is>
+      </c>
+      <c r="P10" s="29" t="inlineStr">
+        <is>
+          <t>40'RH</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="29" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n">
-        <v>1</v>
-      </c>
+      <c r="B11" s="30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="31" t="n"/>
+      <c r="H11" s="31" t="n"/>
       <c r="I11" s="1" t="n"/>
-      <c r="J11" s="29" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="M11" s="30" t="n"/>
-      <c r="N11" s="30" t="n"/>
-      <c r="O11" s="30" t="n"/>
-      <c r="P11" s="30" t="n"/>
+      <c r="J11" s="30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K11" s="31" t="n"/>
+      <c r="L11" s="31" t="n"/>
+      <c r="M11" s="31" t="n"/>
+      <c r="N11" s="31" t="n"/>
+      <c r="O11" s="31" t="n"/>
+      <c r="P11" s="31" t="n"/>
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="30" t="n"/>
+      <c r="B12" s="30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n">
+        <v>1</v>
+      </c>
       <c r="I12" s="1" t="n"/>
-      <c r="J12" s="29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="30" t="n"/>
-      <c r="M12" s="30" t="n"/>
-      <c r="N12" s="30" t="n"/>
-      <c r="O12" s="30" t="n"/>
-      <c r="P12" s="30" t="n"/>
+      <c r="J12" s="30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" s="31" t="n"/>
+      <c r="N12" s="31" t="n"/>
+      <c r="O12" s="31" t="n"/>
+      <c r="P12" s="31" t="n"/>
     </row>
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="29" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C13" s="30" t="n"/>
-      <c r="D13" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
-      <c r="H13" s="30" t="n"/>
+      <c r="B13" s="30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="31" t="n"/>
       <c r="I13" s="1" t="n"/>
-      <c r="J13" s="29" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K13" s="30" t="n"/>
-      <c r="L13" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="30" t="n"/>
-      <c r="N13" s="30" t="n"/>
-      <c r="O13" s="30" t="n"/>
-      <c r="P13" s="30" t="n"/>
+      <c r="J13" s="30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K13" s="31" t="n"/>
+      <c r="L13" s="31" t="n"/>
+      <c r="M13" s="31" t="n"/>
+      <c r="N13" s="31" t="n"/>
+      <c r="O13" s="31" t="n"/>
+      <c r="P13" s="31" t="n"/>
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="29" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C14" s="30" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="30" t="n"/>
-      <c r="H14" s="30" t="n"/>
+      <c r="B14" s="30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="31" t="n"/>
       <c r="I14" s="1" t="n"/>
-      <c r="J14" s="29" t="n">
-        <v>2022</v>
-      </c>
-      <c r="K14" s="30" t="n"/>
-      <c r="L14" s="30" t="n"/>
-      <c r="M14" s="30" t="n"/>
-      <c r="N14" s="30" t="n"/>
-      <c r="O14" s="30" t="n"/>
-      <c r="P14" s="30" t="n"/>
+      <c r="J14" s="30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K14" s="31" t="n"/>
+      <c r="L14" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="31" t="n"/>
+      <c r="N14" s="31" t="n"/>
+      <c r="O14" s="31" t="n"/>
+      <c r="P14" s="31" t="n"/>
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="29" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C15" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="30" t="n"/>
-      <c r="H15" s="30" t="n"/>
+      <c r="B15" s="30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="31" t="n"/>
       <c r="I15" s="1" t="n"/>
-      <c r="J15" s="29" t="n">
-        <v>2021</v>
-      </c>
-      <c r="K15" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" s="30" t="n"/>
-      <c r="N15" s="30" t="n"/>
-      <c r="O15" s="30" t="n"/>
-      <c r="P15" s="30" t="n"/>
+      <c r="J15" s="30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="K15" s="31" t="n"/>
+      <c r="L15" s="31" t="n"/>
+      <c r="M15" s="31" t="n"/>
+      <c r="N15" s="31" t="n"/>
+      <c r="O15" s="31" t="n"/>
+      <c r="P15" s="31" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="31" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C16" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="32" t="n"/>
-      <c r="H16" s="32" t="n"/>
+      <c r="B16" s="30" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="31" t="n"/>
       <c r="I16" s="1" t="n"/>
-      <c r="J16" s="31" t="n">
-        <v>2020</v>
-      </c>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="32" t="n"/>
-      <c r="O16" s="32" t="n"/>
-      <c r="P16" s="32" t="n">
-        <v>1</v>
-      </c>
+      <c r="J16" s="30" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K16" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="31" t="n"/>
+      <c r="N16" s="31" t="n"/>
+      <c r="O16" s="31" t="n"/>
+      <c r="P16" s="31" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="31" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C17" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="32" t="n">
+      <c r="B17" s="32" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="32" t="n"/>
-      <c r="G17" s="32" t="n"/>
-      <c r="H17" s="32" t="n"/>
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="33" t="n"/>
+      <c r="G17" s="33" t="n"/>
+      <c r="H17" s="33" t="n"/>
       <c r="I17" s="1" t="n"/>
-      <c r="J17" s="31" t="n">
-        <v>2019</v>
-      </c>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="M17" s="32" t="n"/>
-      <c r="N17" s="32" t="n"/>
-      <c r="O17" s="32" t="n"/>
-      <c r="P17" s="32" t="n"/>
+      <c r="J17" s="32" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K17" s="33" t="n"/>
+      <c r="L17" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="M17" s="33" t="n"/>
+      <c r="N17" s="33" t="n"/>
+      <c r="O17" s="33" t="n"/>
+      <c r="P17" s="33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="31" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C18" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="32" t="n"/>
-      <c r="H18" s="32" t="n"/>
+      <c r="B18" s="32" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="33" t="n"/>
+      <c r="F18" s="33" t="n"/>
+      <c r="G18" s="33" t="n"/>
+      <c r="H18" s="33" t="n"/>
       <c r="I18" s="1" t="n"/>
-      <c r="J18" s="31" t="n">
-        <v>2018</v>
-      </c>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="32" t="n"/>
-      <c r="M18" s="32" t="n"/>
-      <c r="N18" s="32" t="n"/>
-      <c r="O18" s="32" t="n"/>
-      <c r="P18" s="32" t="n"/>
+      <c r="J18" s="32" t="n">
+        <v>2019</v>
+      </c>
+      <c r="K18" s="33" t="n"/>
+      <c r="L18" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" s="33" t="n"/>
+      <c r="N18" s="33" t="n"/>
+      <c r="O18" s="33" t="n"/>
+      <c r="P18" s="33" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="31" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C19" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
-      <c r="G19" s="32" t="n"/>
-      <c r="H19" s="32" t="n"/>
+      <c r="B19" s="32" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="33" t="n"/>
+      <c r="E19" s="33" t="n"/>
+      <c r="F19" s="33" t="n"/>
+      <c r="G19" s="33" t="n"/>
+      <c r="H19" s="33" t="n"/>
       <c r="I19" s="1" t="n"/>
-      <c r="J19" s="31" t="n">
-        <v>2017</v>
-      </c>
-      <c r="K19" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="32" t="n"/>
-      <c r="N19" s="32" t="n"/>
-      <c r="O19" s="32" t="n"/>
-      <c r="P19" s="32" t="n"/>
+      <c r="J19" s="32" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K19" s="33" t="n"/>
+      <c r="L19" s="33" t="n"/>
+      <c r="M19" s="33" t="n"/>
+      <c r="N19" s="33" t="n"/>
+      <c r="O19" s="33" t="n"/>
+      <c r="P19" s="33" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="31" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C20" s="32" t="n">
+      <c r="B20" s="32" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C20" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="32" t="n">
+      <c r="D20" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="1" t="n"/>
+      <c r="J20" s="32" t="n">
+        <v>2017</v>
+      </c>
+      <c r="K20" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="32" t="n"/>
-      <c r="G20" s="32" t="n"/>
-      <c r="H20" s="32" t="n"/>
-      <c r="I20" s="1" t="n"/>
-      <c r="J20" s="31" t="n">
-        <v>2016</v>
-      </c>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="32" t="n"/>
-      <c r="M20" s="32" t="n"/>
-      <c r="N20" s="32" t="n"/>
-      <c r="O20" s="32" t="n"/>
-      <c r="P20" s="32" t="n"/>
+      <c r="L20" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="33" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="33" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C21" s="34" t="n"/>
-      <c r="D21" s="34" t="n">
+      <c r="B21" s="32" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="34" t="n"/>
-      <c r="G21" s="34" t="n"/>
-      <c r="H21" s="34" t="n"/>
+      <c r="F21" s="33" t="n"/>
+      <c r="G21" s="33" t="n"/>
+      <c r="H21" s="33" t="n"/>
       <c r="I21" s="1" t="n"/>
-      <c r="J21" s="33" t="n">
-        <v>2015</v>
-      </c>
-      <c r="K21" s="34" t="n"/>
-      <c r="L21" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" s="34" t="n"/>
-      <c r="N21" s="34" t="n"/>
-      <c r="O21" s="34" t="n"/>
-      <c r="P21" s="34" t="n"/>
+      <c r="J21" s="32" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K21" s="33" t="n"/>
+      <c r="L21" s="33" t="n"/>
+      <c r="M21" s="33" t="n"/>
+      <c r="N21" s="33" t="n"/>
+      <c r="O21" s="33" t="n"/>
+      <c r="P21" s="33" t="n"/>
     </row>
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="33" t="n">
-        <v>2014</v>
-      </c>
-      <c r="C22" s="34" t="n">
+      <c r="B22" s="34" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="34" t="n"/>
-      <c r="E22" s="34" t="n"/>
-      <c r="F22" s="34" t="n"/>
-      <c r="G22" s="34" t="n"/>
-      <c r="H22" s="34" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="35" t="n"/>
       <c r="I22" s="1" t="n"/>
-      <c r="J22" s="33" t="n">
-        <v>2014</v>
-      </c>
-      <c r="K22" s="34" t="n"/>
-      <c r="L22" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" s="34" t="n"/>
-      <c r="N22" s="34" t="n"/>
-      <c r="O22" s="34" t="n"/>
-      <c r="P22" s="34" t="n"/>
+      <c r="J22" s="34" t="n">
+        <v>2015</v>
+      </c>
+      <c r="K22" s="35" t="n"/>
+      <c r="L22" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="35" t="n"/>
+      <c r="N22" s="35" t="n"/>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="35" t="n"/>
     </row>
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="33" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C23" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="34" t="n"/>
-      <c r="E23" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="F23" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" s="34" t="n">
+      <c r="B23" s="34" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C23" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="34" t="n">
-        <v>1</v>
-      </c>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="35" t="n"/>
       <c r="I23" s="1" t="n"/>
-      <c r="J23" s="33" t="n">
-        <v>2013</v>
-      </c>
-      <c r="K23" s="34" t="n"/>
-      <c r="L23" s="34" t="n"/>
-      <c r="M23" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" s="34" t="n"/>
-      <c r="P23" s="34" t="n"/>
+      <c r="J23" s="34" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K23" s="35" t="n"/>
+      <c r="L23" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M23" s="35" t="n"/>
+      <c r="N23" s="35" t="n"/>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="33" t="n">
-        <v>2012</v>
-      </c>
-      <c r="C24" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="34" t="n">
+      <c r="B24" s="34" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C24" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="34" t="n"/>
-      <c r="G24" s="34" t="n"/>
-      <c r="H24" s="34" t="n"/>
+      <c r="H24" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="I24" s="1" t="n"/>
-      <c r="J24" s="33" t="n">
-        <v>2012</v>
-      </c>
-      <c r="K24" s="34" t="n"/>
-      <c r="L24" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" s="34" t="n"/>
-      <c r="O24" s="34" t="n"/>
-      <c r="P24" s="34" t="n"/>
+      <c r="J24" s="34" t="n">
+        <v>2013</v>
+      </c>
+      <c r="K24" s="35" t="n"/>
+      <c r="L24" s="35" t="n"/>
+      <c r="M24" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="33" t="n">
-        <v>2011</v>
-      </c>
-      <c r="C25" s="34" t="n"/>
-      <c r="D25" s="34" t="n"/>
-      <c r="E25" s="34" t="n"/>
-      <c r="F25" s="34" t="n">
+      <c r="B25" s="34" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C25" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="35" t="n"/>
+      <c r="I25" s="1" t="n"/>
+      <c r="J25" s="34" t="n">
+        <v>2012</v>
+      </c>
+      <c r="K25" s="35" t="n"/>
+      <c r="L25" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="34" t="n"/>
-      <c r="H25" s="34" t="n"/>
-      <c r="I25" s="1" t="n"/>
-      <c r="J25" s="33" t="n">
-        <v>2011</v>
-      </c>
-      <c r="K25" s="34" t="n"/>
-      <c r="L25" s="34" t="n"/>
-      <c r="M25" s="34" t="n"/>
-      <c r="N25" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" s="34" t="n"/>
-      <c r="P25" s="34" t="n"/>
+      <c r="M25" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="35" t="n"/>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="35" t="n"/>
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="35" t="n">
-        <v>2010</v>
-      </c>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
+      <c r="B26" s="34" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
       <c r="I26" s="1" t="n"/>
-      <c r="J26" s="35" t="n">
-        <v>2010</v>
-      </c>
-      <c r="K26" s="36" t="n"/>
-      <c r="L26" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" s="36" t="n"/>
-      <c r="N26" s="36" t="n"/>
-      <c r="O26" s="36" t="n"/>
-      <c r="P26" s="36" t="n"/>
+      <c r="J26" s="34" t="n">
+        <v>2011</v>
+      </c>
+      <c r="K26" s="35" t="n"/>
+      <c r="L26" s="35" t="n"/>
+      <c r="M26" s="35" t="n"/>
+      <c r="N26" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="35" t="n"/>
     </row>
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="36" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="37" t="n"/>
+      <c r="G27" s="37" t="n"/>
+      <c r="H27" s="37" t="n"/>
+      <c r="I27" s="1" t="n"/>
+      <c r="J27" s="36" t="n">
+        <v>2010</v>
+      </c>
+      <c r="K27" s="37" t="n"/>
+      <c r="L27" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="37" t="n"/>
+      <c r="N27" s="37" t="n"/>
+      <c r="O27" s="37" t="n"/>
+      <c r="P27" s="37" t="n"/>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>GTTL</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C28" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D28" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E28" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F28" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G28" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H28" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="I28" s="1" t="n"/>
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>GTTL</t>
         </is>
       </c>
-      <c r="K27" s="13" t="n">
+      <c r="K28" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="L27" s="13" t="n">
+      <c r="L28" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="M27" s="13" t="n">
+      <c r="M28" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="N27" s="13" t="n">
+      <c r="N28" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="O27" s="13" t="n"/>
-      <c r="P27" s="13" t="n">
+      <c r="O28" s="17" t="n"/>
+      <c r="P28" s="17" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="E9:F9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -7267,7 +7342,7 @@
   <sheetData>
     <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="37">
+      <c r="B1" s="38">
         <f>'TOTAL RH'!A1</f>
         <v/>
       </c>
@@ -7303,29 +7378,29 @@
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>SHORTFALL ALERT</t>
         </is>
       </c>
-      <c r="C4" s="23" t="n"/>
-      <c r="D4" s="23" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
       <c r="E4" s="1" t="n"/>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
         <is>
           <t>COMBINED 40'RH STOCK</t>
         </is>
       </c>
-      <c r="G4" s="23" t="n"/>
-      <c r="H4" s="23" t="n"/>
+      <c r="G4" s="24" t="n"/>
+      <c r="H4" s="24" t="n"/>
       <c r="I4" s="1" t="n"/>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="J4" s="40" t="inlineStr">
         <is>
           <t>COMBINED 40'RH BOOKING</t>
         </is>
       </c>
-      <c r="K4" s="23" t="n"/>
-      <c r="L4" s="23" t="n"/>
+      <c r="K4" s="24" t="n"/>
+      <c r="L4" s="24" t="n"/>
       <c r="M4" s="1" t="n"/>
       <c r="N4" s="1" t="n"/>
       <c r="O4" s="1" t="n"/>
@@ -7333,26 +7408,26 @@
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="40">
-        <f>MIN('TOTAL RH'!D12,'TOTAL RH'!J12)</f>
-        <v/>
-      </c>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
+      <c r="B5" s="41">
+        <f>MIN('TOTAL RH'!D15,'TOTAL RH'!J15)</f>
+        <v/>
+      </c>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
       <c r="E5" s="1" t="n"/>
-      <c r="F5" s="41">
-        <f>'TOTAL RH'!O5</f>
-        <v/>
-      </c>
-      <c r="G5" s="23" t="n"/>
-      <c r="H5" s="23" t="n"/>
+      <c r="F5" s="42">
+        <f>'TOTAL RH'!O6</f>
+        <v/>
+      </c>
+      <c r="G5" s="24" t="n"/>
+      <c r="H5" s="24" t="n"/>
       <c r="I5" s="1" t="n"/>
-      <c r="J5" s="41">
-        <f>'TOTAL RH'!O10</f>
-        <v/>
-      </c>
-      <c r="K5" s="23" t="n"/>
-      <c r="L5" s="23" t="n"/>
+      <c r="J5" s="42">
+        <f>'TOTAL RH'!O11</f>
+        <v/>
+      </c>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="24" t="n"/>
       <c r="M5" s="1" t="n"/>
       <c r="N5" s="1" t="n"/>
       <c r="O5" s="1" t="n"/>
@@ -7360,28 +7435,28 @@
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="42">
-        <f>"BKK27/LCH27 40'RH, worse "&amp;'TOTAL RH'!B12</f>
-        <v/>
-      </c>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
+      <c r="B6" s="43">
+        <f>"BKK27/LCH27 40'RH, worse "&amp;'TOTAL RH'!B15</f>
+        <v/>
+      </c>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
       <c r="E6" s="1" t="n"/>
-      <c r="F6" s="42" t="inlineStr">
+      <c r="F6" s="43" t="inlineStr">
         <is>
           <t>BKK27 + LCH27</t>
         </is>
       </c>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="23" t="n"/>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="24" t="n"/>
       <c r="I6" s="1" t="n"/>
-      <c r="J6" s="42" t="inlineStr">
+      <c r="J6" s="43" t="inlineStr">
         <is>
           <t>pending + all weeks</t>
         </is>
       </c>
-      <c r="K6" s="23" t="n"/>
-      <c r="L6" s="23" t="n"/>
+      <c r="K6" s="24" t="n"/>
+      <c r="L6" s="24" t="n"/>
       <c r="M6" s="1" t="n"/>
       <c r="N6" s="1" t="n"/>
       <c r="O6" s="1" t="n"/>
@@ -7407,7 +7482,7 @@
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>DETAIL BY DEPOT</t>
         </is>
@@ -7429,21 +7504,21 @@
     </row>
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="44">
-        <f>'TOTAL RH'!B2</f>
-        <v/>
-      </c>
-      <c r="C9" s="61" t="n"/>
-      <c r="D9" s="62" t="n"/>
+      <c r="B9" s="45">
+        <f>'TOTAL RH'!B3</f>
+        <v/>
+      </c>
+      <c r="C9" s="62" t="n"/>
+      <c r="D9" s="63" t="n"/>
       <c r="E9" s="1" t="n"/>
       <c r="F9" s="1" t="n"/>
       <c r="G9" s="1" t="n"/>
-      <c r="H9" s="45">
-        <f>'TOTAL RH'!H2</f>
-        <v/>
-      </c>
-      <c r="I9" s="61" t="n"/>
-      <c r="J9" s="62" t="n"/>
+      <c r="H9" s="46">
+        <f>'TOTAL RH'!H3</f>
+        <v/>
+      </c>
+      <c r="I9" s="62" t="n"/>
+      <c r="J9" s="63" t="n"/>
       <c r="K9" s="1" t="n"/>
       <c r="L9" s="1" t="n"/>
       <c r="M9" s="1" t="n"/>
@@ -7453,13 +7528,13 @@
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>20'RE</t>
         </is>
       </c>
-      <c r="D10" s="46" t="inlineStr">
+      <c r="D10" s="47" t="inlineStr">
         <is>
           <t>40'RH</t>
         </is>
@@ -7467,13 +7542,13 @@
       <c r="E10" s="1" t="n"/>
       <c r="F10" s="1" t="n"/>
       <c r="G10" s="1" t="n"/>
-      <c r="H10" s="23" t="n"/>
-      <c r="I10" s="46" t="inlineStr">
+      <c r="H10" s="24" t="n"/>
+      <c r="I10" s="47" t="inlineStr">
         <is>
           <t>20'RE</t>
         </is>
       </c>
-      <c r="J10" s="46" t="inlineStr">
+      <c r="J10" s="47" t="inlineStr">
         <is>
           <t>40'RH</t>
         </is>
@@ -7487,31 +7562,31 @@
     </row>
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="47">
-        <f>'TOTAL RH'!B4</f>
-        <v/>
-      </c>
-      <c r="C11" s="48">
-        <f>'TOTAL RH'!C4</f>
-        <v/>
-      </c>
-      <c r="D11" s="48">
-        <f>'TOTAL RH'!D4</f>
+      <c r="B11" s="48">
+        <f>'TOTAL RH'!B5</f>
+        <v/>
+      </c>
+      <c r="C11" s="49">
+        <f>'TOTAL RH'!C5</f>
+        <v/>
+      </c>
+      <c r="D11" s="49">
+        <f>'TOTAL RH'!D5</f>
         <v/>
       </c>
       <c r="E11" s="1" t="n"/>
       <c r="F11" s="1" t="n"/>
       <c r="G11" s="1" t="n"/>
-      <c r="H11" s="47">
-        <f>'TOTAL RH'!H4</f>
-        <v/>
-      </c>
-      <c r="I11" s="48">
-        <f>'TOTAL RH'!I4</f>
-        <v/>
-      </c>
-      <c r="J11" s="48">
-        <f>'TOTAL RH'!J4</f>
+      <c r="H11" s="48">
+        <f>'TOTAL RH'!H5</f>
+        <v/>
+      </c>
+      <c r="I11" s="49">
+        <f>'TOTAL RH'!I5</f>
+        <v/>
+      </c>
+      <c r="J11" s="49">
+        <f>'TOTAL RH'!J5</f>
         <v/>
       </c>
       <c r="K11" s="1" t="n"/>
@@ -7523,31 +7598,31 @@
     </row>
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="49">
-        <f>'TOTAL RH'!B5</f>
-        <v/>
-      </c>
-      <c r="C12" s="50">
-        <f>'TOTAL RH'!C5</f>
-        <v/>
-      </c>
-      <c r="D12" s="50">
-        <f>'TOTAL RH'!D5</f>
+      <c r="B12" s="50">
+        <f>'TOTAL RH'!B6</f>
+        <v/>
+      </c>
+      <c r="C12" s="51">
+        <f>'TOTAL RH'!C6</f>
+        <v/>
+      </c>
+      <c r="D12" s="51">
+        <f>'TOTAL RH'!D6</f>
         <v/>
       </c>
       <c r="E12" s="1" t="n"/>
       <c r="F12" s="1" t="n"/>
       <c r="G12" s="1" t="n"/>
-      <c r="H12" s="49">
-        <f>'TOTAL RH'!H5</f>
-        <v/>
-      </c>
-      <c r="I12" s="50">
-        <f>'TOTAL RH'!I5</f>
-        <v/>
-      </c>
-      <c r="J12" s="50">
-        <f>'TOTAL RH'!J5</f>
+      <c r="H12" s="50">
+        <f>'TOTAL RH'!H6</f>
+        <v/>
+      </c>
+      <c r="I12" s="51">
+        <f>'TOTAL RH'!I6</f>
+        <v/>
+      </c>
+      <c r="J12" s="51">
+        <f>'TOTAL RH'!J6</f>
         <v/>
       </c>
       <c r="K12" s="1" t="n"/>
@@ -7559,31 +7634,31 @@
     </row>
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="49">
-        <f>'TOTAL RH'!B6</f>
-        <v/>
-      </c>
-      <c r="C13" s="50">
-        <f>'TOTAL RH'!C6</f>
-        <v/>
-      </c>
-      <c r="D13" s="50">
-        <f>'TOTAL RH'!D6</f>
+      <c r="B13" s="50">
+        <f>'TOTAL RH'!B7</f>
+        <v/>
+      </c>
+      <c r="C13" s="51">
+        <f>'TOTAL RH'!C7</f>
+        <v/>
+      </c>
+      <c r="D13" s="51">
+        <f>'TOTAL RH'!D7</f>
         <v/>
       </c>
       <c r="E13" s="1" t="n"/>
       <c r="F13" s="1" t="n"/>
       <c r="G13" s="1" t="n"/>
-      <c r="H13" s="49">
-        <f>'TOTAL RH'!H6</f>
-        <v/>
-      </c>
-      <c r="I13" s="50">
-        <f>'TOTAL RH'!I6</f>
-        <v/>
-      </c>
-      <c r="J13" s="50">
-        <f>'TOTAL RH'!J6</f>
+      <c r="H13" s="50">
+        <f>'TOTAL RH'!H7</f>
+        <v/>
+      </c>
+      <c r="I13" s="51">
+        <f>'TOTAL RH'!I7</f>
+        <v/>
+      </c>
+      <c r="J13" s="51">
+        <f>'TOTAL RH'!J7</f>
         <v/>
       </c>
       <c r="K13" s="1" t="n"/>
@@ -7595,31 +7670,31 @@
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="49">
-        <f>'TOTAL RH'!B7</f>
-        <v/>
-      </c>
-      <c r="C14" s="50">
-        <f>'TOTAL RH'!C7</f>
-        <v/>
-      </c>
-      <c r="D14" s="50">
-        <f>'TOTAL RH'!D7</f>
+      <c r="B14" s="50">
+        <f>'TOTAL RH'!B8</f>
+        <v/>
+      </c>
+      <c r="C14" s="51">
+        <f>'TOTAL RH'!C8</f>
+        <v/>
+      </c>
+      <c r="D14" s="51">
+        <f>'TOTAL RH'!D8</f>
         <v/>
       </c>
       <c r="E14" s="1" t="n"/>
       <c r="F14" s="1" t="n"/>
       <c r="G14" s="1" t="n"/>
-      <c r="H14" s="49">
-        <f>'TOTAL RH'!H7</f>
-        <v/>
-      </c>
-      <c r="I14" s="50">
-        <f>'TOTAL RH'!I7</f>
-        <v/>
-      </c>
-      <c r="J14" s="50">
-        <f>'TOTAL RH'!J7</f>
+      <c r="H14" s="50">
+        <f>'TOTAL RH'!H8</f>
+        <v/>
+      </c>
+      <c r="I14" s="51">
+        <f>'TOTAL RH'!I8</f>
+        <v/>
+      </c>
+      <c r="J14" s="51">
+        <f>'TOTAL RH'!J8</f>
         <v/>
       </c>
       <c r="K14" s="1" t="n"/>
@@ -7631,31 +7706,31 @@
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="51">
-        <f>'TOTAL RH'!B8</f>
-        <v/>
-      </c>
-      <c r="C15" s="52">
-        <f>'TOTAL RH'!C8</f>
-        <v/>
-      </c>
-      <c r="D15" s="52">
-        <f>'TOTAL RH'!D8</f>
+      <c r="B15" s="52">
+        <f>'TOTAL RH'!B9</f>
+        <v/>
+      </c>
+      <c r="C15" s="53">
+        <f>'TOTAL RH'!C9</f>
+        <v/>
+      </c>
+      <c r="D15" s="53">
+        <f>'TOTAL RH'!D9</f>
         <v/>
       </c>
       <c r="E15" s="1" t="n"/>
       <c r="F15" s="1" t="n"/>
       <c r="G15" s="1" t="n"/>
-      <c r="H15" s="51">
-        <f>'TOTAL RH'!H8</f>
-        <v/>
-      </c>
-      <c r="I15" s="52">
-        <f>'TOTAL RH'!I8</f>
-        <v/>
-      </c>
-      <c r="J15" s="52">
-        <f>'TOTAL RH'!J8</f>
+      <c r="H15" s="52">
+        <f>'TOTAL RH'!H9</f>
+        <v/>
+      </c>
+      <c r="I15" s="53">
+        <f>'TOTAL RH'!I9</f>
+        <v/>
+      </c>
+      <c r="J15" s="53">
+        <f>'TOTAL RH'!J9</f>
         <v/>
       </c>
       <c r="K15" s="1" t="n"/>
@@ -7685,31 +7760,31 @@
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="49">
-        <f>'TOTAL RH'!B9</f>
-        <v/>
-      </c>
-      <c r="C17" s="50">
-        <f>'TOTAL RH'!C9</f>
-        <v/>
-      </c>
-      <c r="D17" s="50">
-        <f>'TOTAL RH'!D9</f>
+      <c r="B17" s="50">
+        <f>'TOTAL RH'!B11</f>
+        <v/>
+      </c>
+      <c r="C17" s="51">
+        <f>'TOTAL RH'!C11</f>
+        <v/>
+      </c>
+      <c r="D17" s="51">
+        <f>'TOTAL RH'!D11</f>
         <v/>
       </c>
       <c r="E17" s="1" t="n"/>
       <c r="F17" s="1" t="n"/>
       <c r="G17" s="1" t="n"/>
-      <c r="H17" s="49">
-        <f>'TOTAL RH'!H9</f>
-        <v/>
-      </c>
-      <c r="I17" s="50">
-        <f>'TOTAL RH'!I9</f>
-        <v/>
-      </c>
-      <c r="J17" s="50">
-        <f>'TOTAL RH'!J9</f>
+      <c r="H17" s="50">
+        <f>'TOTAL RH'!H11</f>
+        <v/>
+      </c>
+      <c r="I17" s="51">
+        <f>'TOTAL RH'!I11</f>
+        <v/>
+      </c>
+      <c r="J17" s="51">
+        <f>'TOTAL RH'!J11</f>
         <v/>
       </c>
       <c r="K17" s="1" t="n"/>
@@ -7721,31 +7796,31 @@
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="51">
-        <f>'TOTAL RH'!B10</f>
-        <v/>
-      </c>
-      <c r="C18" s="52">
-        <f>'TOTAL RH'!C10</f>
-        <v/>
-      </c>
-      <c r="D18" s="52">
-        <f>'TOTAL RH'!D10</f>
+      <c r="B18" s="52">
+        <f>'TOTAL RH'!B12</f>
+        <v/>
+      </c>
+      <c r="C18" s="53">
+        <f>'TOTAL RH'!C12</f>
+        <v/>
+      </c>
+      <c r="D18" s="53">
+        <f>'TOTAL RH'!D12</f>
         <v/>
       </c>
       <c r="E18" s="1" t="n"/>
       <c r="F18" s="1" t="n"/>
       <c r="G18" s="1" t="n"/>
-      <c r="H18" s="51">
-        <f>'TOTAL RH'!H10</f>
-        <v/>
-      </c>
-      <c r="I18" s="52">
-        <f>'TOTAL RH'!I10</f>
-        <v/>
-      </c>
-      <c r="J18" s="63">
-        <f>'TOTAL RH'!J10</f>
+      <c r="H18" s="52">
+        <f>'TOTAL RH'!H12</f>
+        <v/>
+      </c>
+      <c r="I18" s="53">
+        <f>'TOTAL RH'!I12</f>
+        <v/>
+      </c>
+      <c r="J18" s="64">
+        <f>'TOTAL RH'!J12</f>
         <v/>
       </c>
       <c r="K18" s="1" t="n"/>
@@ -7775,31 +7850,31 @@
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="49">
-        <f>'TOTAL RH'!B11</f>
-        <v/>
-      </c>
-      <c r="C20" s="50">
-        <f>'TOTAL RH'!C11</f>
-        <v/>
-      </c>
-      <c r="D20" s="50">
-        <f>'TOTAL RH'!D11</f>
+      <c r="B20" s="50">
+        <f>'TOTAL RH'!B14</f>
+        <v/>
+      </c>
+      <c r="C20" s="51">
+        <f>'TOTAL RH'!C14</f>
+        <v/>
+      </c>
+      <c r="D20" s="51">
+        <f>'TOTAL RH'!D14</f>
         <v/>
       </c>
       <c r="E20" s="1" t="n"/>
       <c r="F20" s="1" t="n"/>
       <c r="G20" s="1" t="n"/>
-      <c r="H20" s="49">
-        <f>'TOTAL RH'!H11</f>
-        <v/>
-      </c>
-      <c r="I20" s="50">
-        <f>'TOTAL RH'!I11</f>
-        <v/>
-      </c>
-      <c r="J20" s="50">
-        <f>'TOTAL RH'!J11</f>
+      <c r="H20" s="50">
+        <f>'TOTAL RH'!H14</f>
+        <v/>
+      </c>
+      <c r="I20" s="51">
+        <f>'TOTAL RH'!I14</f>
+        <v/>
+      </c>
+      <c r="J20" s="51">
+        <f>'TOTAL RH'!J14</f>
         <v/>
       </c>
       <c r="K20" s="1" t="n"/>
@@ -7811,31 +7886,31 @@
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="51">
-        <f>'TOTAL RH'!B12</f>
-        <v/>
-      </c>
-      <c r="C21" s="52">
-        <f>'TOTAL RH'!C12</f>
-        <v/>
-      </c>
-      <c r="D21" s="63">
-        <f>'TOTAL RH'!D12</f>
+      <c r="B21" s="52">
+        <f>'TOTAL RH'!B15</f>
+        <v/>
+      </c>
+      <c r="C21" s="53">
+        <f>'TOTAL RH'!C15</f>
+        <v/>
+      </c>
+      <c r="D21" s="64">
+        <f>'TOTAL RH'!D15</f>
         <v/>
       </c>
       <c r="E21" s="1" t="n"/>
       <c r="F21" s="1" t="n"/>
       <c r="G21" s="1" t="n"/>
-      <c r="H21" s="51">
-        <f>'TOTAL RH'!H12</f>
-        <v/>
-      </c>
-      <c r="I21" s="52">
-        <f>'TOTAL RH'!I12</f>
-        <v/>
-      </c>
-      <c r="J21" s="63">
-        <f>'TOTAL RH'!J12</f>
+      <c r="H21" s="52">
+        <f>'TOTAL RH'!H15</f>
+        <v/>
+      </c>
+      <c r="I21" s="53">
+        <f>'TOTAL RH'!I15</f>
+        <v/>
+      </c>
+      <c r="J21" s="64">
+        <f>'TOTAL RH'!J15</f>
         <v/>
       </c>
       <c r="K21" s="1" t="n"/>
@@ -7883,7 +7958,7 @@
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="43" t="inlineStr">
+      <c r="B24" s="44" t="inlineStr">
         <is>
           <t>REMARKS  (AV = move code IED/IEP/IER, DMG = move code OER)</t>
         </is>
@@ -7905,21 +7980,21 @@
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="44">
-        <f>'TOTAL RH'!B2</f>
-        <v/>
-      </c>
-      <c r="C25" s="61" t="n"/>
-      <c r="D25" s="62" t="n"/>
+      <c r="B25" s="45">
+        <f>'TOTAL RH'!B3</f>
+        <v/>
+      </c>
+      <c r="C25" s="62" t="n"/>
+      <c r="D25" s="63" t="n"/>
       <c r="E25" s="1" t="n"/>
       <c r="F25" s="1" t="n"/>
       <c r="G25" s="1" t="n"/>
-      <c r="H25" s="45">
-        <f>'TOTAL RH'!H2</f>
-        <v/>
-      </c>
-      <c r="I25" s="61" t="n"/>
-      <c r="J25" s="62" t="n"/>
+      <c r="H25" s="46">
+        <f>'TOTAL RH'!H3</f>
+        <v/>
+      </c>
+      <c r="I25" s="62" t="n"/>
+      <c r="J25" s="63" t="n"/>
       <c r="K25" s="1" t="n"/>
       <c r="L25" s="1" t="n"/>
       <c r="M25" s="1" t="n"/>
@@ -7929,13 +8004,13 @@
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>20'RE</t>
         </is>
       </c>
-      <c r="D26" s="46" t="inlineStr">
+      <c r="D26" s="47" t="inlineStr">
         <is>
           <t>40'RH</t>
         </is>
@@ -7943,13 +8018,13 @@
       <c r="E26" s="1" t="n"/>
       <c r="F26" s="1" t="n"/>
       <c r="G26" s="1" t="n"/>
-      <c r="H26" s="23" t="n"/>
-      <c r="I26" s="46" t="inlineStr">
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="47" t="inlineStr">
         <is>
           <t>20'RE</t>
         </is>
       </c>
-      <c r="J26" s="46" t="inlineStr">
+      <c r="J26" s="47" t="inlineStr">
         <is>
           <t>40'RH</t>
         </is>
@@ -7963,33 +8038,33 @@
     </row>
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>AV</t>
         </is>
       </c>
-      <c r="C27" s="50">
-        <f>'TOTAL RH'!C16</f>
-        <v/>
-      </c>
-      <c r="D27" s="50">
-        <f>'TOTAL RH'!D16</f>
+      <c r="C27" s="51">
+        <f>'TOTAL RH'!C19</f>
+        <v/>
+      </c>
+      <c r="D27" s="51">
+        <f>'TOTAL RH'!D19</f>
         <v/>
       </c>
       <c r="E27" s="1" t="n"/>
       <c r="F27" s="1" t="n"/>
       <c r="G27" s="1" t="n"/>
-      <c r="H27" s="23" t="inlineStr">
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>AV</t>
         </is>
       </c>
-      <c r="I27" s="50">
-        <f>'TOTAL RH'!I16</f>
-        <v/>
-      </c>
-      <c r="J27" s="50">
-        <f>'TOTAL RH'!J16</f>
+      <c r="I27" s="51">
+        <f>'TOTAL RH'!I19</f>
+        <v/>
+      </c>
+      <c r="J27" s="51">
+        <f>'TOTAL RH'!J19</f>
         <v/>
       </c>
       <c r="K27" s="1" t="n"/>
@@ -8001,33 +8076,33 @@
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>DMG</t>
         </is>
       </c>
-      <c r="C28" s="50">
-        <f>'TOTAL RH'!C17</f>
-        <v/>
-      </c>
-      <c r="D28" s="50">
-        <f>'TOTAL RH'!D17</f>
+      <c r="C28" s="51">
+        <f>'TOTAL RH'!C20</f>
+        <v/>
+      </c>
+      <c r="D28" s="51">
+        <f>'TOTAL RH'!D20</f>
         <v/>
       </c>
       <c r="E28" s="1" t="n"/>
       <c r="F28" s="1" t="n"/>
       <c r="G28" s="1" t="n"/>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>DMG</t>
         </is>
       </c>
-      <c r="I28" s="50">
-        <f>'TOTAL RH'!I17</f>
-        <v/>
-      </c>
-      <c r="J28" s="50">
-        <f>'TOTAL RH'!J17</f>
+      <c r="I28" s="51">
+        <f>'TOTAL RH'!I20</f>
+        <v/>
+      </c>
+      <c r="J28" s="51">
+        <f>'TOTAL RH'!J20</f>
         <v/>
       </c>
       <c r="K28" s="1" t="n"/>
@@ -8075,7 +8150,7 @@
     </row>
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="43" t="inlineStr">
+      <c r="B31" s="44" t="inlineStr">
         <is>
           <t>RF SEASONAL — build year</t>
         </is>
@@ -8097,29 +8172,29 @@
     </row>
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>BKK27 2020-26 BUILT</t>
         </is>
       </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
       <c r="E32" s="1" t="n"/>
-      <c r="F32" s="39" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>LCH27 2020-26 BUILT</t>
         </is>
       </c>
-      <c r="G32" s="23" t="n"/>
-      <c r="H32" s="23" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="n"/>
       <c r="I32" s="1" t="n"/>
-      <c r="J32" s="39" t="inlineStr">
+      <c r="J32" s="40" t="inlineStr">
         <is>
           <t>PEAK BUILD YEAR</t>
         </is>
       </c>
-      <c r="K32" s="23" t="n"/>
-      <c r="L32" s="23" t="n"/>
+      <c r="K32" s="24" t="n"/>
+      <c r="L32" s="24" t="n"/>
       <c r="M32" s="1" t="n"/>
       <c r="N32" s="1" t="n"/>
       <c r="O32" s="1" t="n"/>
@@ -8127,26 +8202,26 @@
     </row>
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="53">
-        <f>SUM('YEAR BUILT'!D10:D16)+SUM('YEAR BUILT'!F10:F16)+SUM('YEAR BUILT'!H10:H16)</f>
-        <v/>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="23" t="n"/>
+      <c r="B33" s="54">
+        <f>SUM('YEAR BUILT'!D11:D17)+SUM('YEAR BUILT'!F11:F17)+SUM('YEAR BUILT'!H11:H17)</f>
+        <v/>
+      </c>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
       <c r="E33" s="1" t="n"/>
-      <c r="F33" s="54">
-        <f>SUM('YEAR BUILT'!L10:L16)+SUM('YEAR BUILT'!N10:N16)+SUM('YEAR BUILT'!P10:P16)</f>
-        <v/>
-      </c>
-      <c r="G33" s="23" t="n"/>
-      <c r="H33" s="23" t="n"/>
+      <c r="F33" s="55">
+        <f>SUM('YEAR BUILT'!L11:L17)+SUM('YEAR BUILT'!N11:N17)+SUM('YEAR BUILT'!P11:P17)</f>
+        <v/>
+      </c>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="24" t="n"/>
       <c r="I33" s="1" t="n"/>
-      <c r="J33" s="41">
+      <c r="J33" s="42">
         <f>"2020"</f>
         <v/>
       </c>
-      <c r="K33" s="23" t="n"/>
-      <c r="L33" s="23" t="n"/>
+      <c r="K33" s="24" t="n"/>
+      <c r="L33" s="24" t="n"/>
       <c r="M33" s="1" t="n"/>
       <c r="N33" s="1" t="n"/>
       <c r="O33" s="1" t="n"/>
@@ -8154,29 +8229,29 @@
     </row>
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="42" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>of 40'RH on hand</t>
         </is>
       </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
       <c r="E34" s="1" t="n"/>
-      <c r="F34" s="42" t="inlineStr">
+      <c r="F34" s="43" t="inlineStr">
         <is>
           <t>of 40'RH on hand</t>
         </is>
       </c>
-      <c r="G34" s="23" t="n"/>
-      <c r="H34" s="23" t="n"/>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="n"/>
       <c r="I34" s="1" t="n"/>
-      <c r="J34" s="42" t="inlineStr">
+      <c r="J34" s="43" t="inlineStr">
         <is>
           <t>17 units across both depots</t>
         </is>
       </c>
-      <c r="K34" s="23" t="n"/>
-      <c r="L34" s="23" t="n"/>
+      <c r="K34" s="24" t="n"/>
+      <c r="L34" s="24" t="n"/>
       <c r="M34" s="1" t="n"/>
       <c r="N34" s="1" t="n"/>
       <c r="O34" s="1" t="n"/>
@@ -8202,101 +8277,101 @@
     </row>
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>BKK27 DURIAN  (2021-2026)</t>
         </is>
       </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
       <c r="E36" s="1" t="n"/>
-      <c r="F36" s="39" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>BKK27 NON DURIAN  (≤ 2020)</t>
         </is>
       </c>
-      <c r="G36" s="23" t="n"/>
-      <c r="H36" s="23" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
       <c r="I36" s="1" t="n"/>
-      <c r="J36" s="39" t="inlineStr">
+      <c r="J36" s="40" t="inlineStr">
         <is>
           <t>LCH27 DURIAN  (2021-2026)</t>
         </is>
       </c>
-      <c r="K36" s="23" t="n"/>
-      <c r="L36" s="23" t="n"/>
+      <c r="K36" s="24" t="n"/>
+      <c r="L36" s="24" t="n"/>
       <c r="M36" s="1" t="n"/>
-      <c r="N36" s="39" t="inlineStr">
+      <c r="N36" s="40" t="inlineStr">
         <is>
           <t>LCH27 NON DURIAN  (≤ 2020)</t>
         </is>
       </c>
-      <c r="O36" s="23" t="n"/>
-      <c r="P36" s="23" t="n"/>
+      <c r="O36" s="24" t="n"/>
+      <c r="P36" s="24" t="n"/>
     </row>
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="53">
-        <f>'YEAR BUILT'!B3</f>
-        <v/>
-      </c>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="23" t="n"/>
+      <c r="B37" s="54">
+        <f>'YEAR BUILT'!B4</f>
+        <v/>
+      </c>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
       <c r="E37" s="1" t="n"/>
-      <c r="F37" s="53">
-        <f>'YEAR BUILT'!F3</f>
-        <v/>
-      </c>
-      <c r="G37" s="23" t="n"/>
-      <c r="H37" s="23" t="n"/>
+      <c r="F37" s="54">
+        <f>'YEAR BUILT'!F4</f>
+        <v/>
+      </c>
+      <c r="G37" s="24" t="n"/>
+      <c r="H37" s="24" t="n"/>
       <c r="I37" s="1" t="n"/>
-      <c r="J37" s="54">
-        <f>'YEAR BUILT'!J3</f>
-        <v/>
-      </c>
-      <c r="K37" s="23" t="n"/>
-      <c r="L37" s="23" t="n"/>
+      <c r="J37" s="55">
+        <f>'YEAR BUILT'!J4</f>
+        <v/>
+      </c>
+      <c r="K37" s="24" t="n"/>
+      <c r="L37" s="24" t="n"/>
       <c r="M37" s="1" t="n"/>
-      <c r="N37" s="54">
-        <f>'YEAR BUILT'!N3</f>
-        <v/>
-      </c>
-      <c r="O37" s="23" t="n"/>
-      <c r="P37" s="23" t="n"/>
+      <c r="N37" s="55">
+        <f>'YEAR BUILT'!N4</f>
+        <v/>
+      </c>
+      <c r="O37" s="24" t="n"/>
+      <c r="P37" s="24" t="n"/>
     </row>
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="42" t="inlineStr">
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>40'RH stock</t>
         </is>
       </c>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="23" t="n"/>
+      <c r="C38" s="24" t="n"/>
+      <c r="D38" s="24" t="n"/>
       <c r="E38" s="1" t="n"/>
-      <c r="F38" s="42" t="inlineStr">
+      <c r="F38" s="43" t="inlineStr">
         <is>
           <t>40'RH stock</t>
         </is>
       </c>
-      <c r="G38" s="23" t="n"/>
-      <c r="H38" s="23" t="n"/>
+      <c r="G38" s="24" t="n"/>
+      <c r="H38" s="24" t="n"/>
       <c r="I38" s="1" t="n"/>
-      <c r="J38" s="42" t="inlineStr">
+      <c r="J38" s="43" t="inlineStr">
         <is>
           <t>40'RH stock</t>
         </is>
       </c>
-      <c r="K38" s="23" t="n"/>
-      <c r="L38" s="23" t="n"/>
+      <c r="K38" s="24" t="n"/>
+      <c r="L38" s="24" t="n"/>
       <c r="M38" s="1" t="n"/>
-      <c r="N38" s="42" t="inlineStr">
+      <c r="N38" s="43" t="inlineStr">
         <is>
           <t>40'RH stock</t>
         </is>
       </c>
-      <c r="O38" s="23" t="n"/>
-      <c r="P38" s="23" t="n"/>
+      <c r="O38" s="24" t="n"/>
+      <c r="P38" s="24" t="n"/>
     </row>
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="1" t="n"/>
@@ -8318,23 +8393,23 @@
     </row>
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="44" t="inlineStr">
+      <c r="B40" s="45" t="inlineStr">
         <is>
           <t>BKK27 current mix</t>
         </is>
       </c>
-      <c r="C40" s="61" t="n"/>
-      <c r="D40" s="62" t="n"/>
+      <c r="C40" s="62" t="n"/>
+      <c r="D40" s="63" t="n"/>
       <c r="E40" s="1" t="n"/>
       <c r="F40" s="1" t="n"/>
       <c r="G40" s="1" t="n"/>
-      <c r="H40" s="45" t="inlineStr">
+      <c r="H40" s="46" t="inlineStr">
         <is>
           <t>LCH27 current mix</t>
         </is>
       </c>
-      <c r="I40" s="61" t="n"/>
-      <c r="J40" s="62" t="n"/>
+      <c r="I40" s="62" t="n"/>
+      <c r="J40" s="63" t="n"/>
       <c r="K40" s="1" t="n"/>
       <c r="L40" s="1" t="n"/>
       <c r="M40" s="1" t="n"/>
@@ -8344,13 +8419,13 @@
     </row>
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="23" t="n"/>
-      <c r="C41" s="46" t="inlineStr">
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="47" t="inlineStr">
         <is>
           <t>22RE</t>
         </is>
       </c>
-      <c r="D41" s="46" t="inlineStr">
+      <c r="D41" s="47" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
@@ -8358,13 +8433,13 @@
       <c r="E41" s="1" t="n"/>
       <c r="F41" s="1" t="n"/>
       <c r="G41" s="1" t="n"/>
-      <c r="H41" s="23" t="n"/>
-      <c r="I41" s="46" t="inlineStr">
+      <c r="H41" s="24" t="n"/>
+      <c r="I41" s="47" t="inlineStr">
         <is>
           <t>22RE</t>
         </is>
       </c>
-      <c r="J41" s="46" t="inlineStr">
+      <c r="J41" s="47" t="inlineStr">
         <is>
           <t>45RE</t>
         </is>
@@ -8378,33 +8453,33 @@
     </row>
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>CARRIER</t>
         </is>
       </c>
-      <c r="C42" s="50">
-        <f>'YEAR BUILT'!C27</f>
-        <v/>
-      </c>
-      <c r="D42" s="50">
-        <f>'YEAR BUILT'!D27</f>
+      <c r="C42" s="51">
+        <f>'YEAR BUILT'!C28</f>
+        <v/>
+      </c>
+      <c r="D42" s="51">
+        <f>'YEAR BUILT'!D28</f>
         <v/>
       </c>
       <c r="E42" s="1" t="n"/>
       <c r="F42" s="1" t="n"/>
       <c r="G42" s="1" t="n"/>
-      <c r="H42" s="23" t="inlineStr">
+      <c r="H42" s="24" t="inlineStr">
         <is>
           <t>CARRIER</t>
         </is>
       </c>
-      <c r="I42" s="50">
-        <f>'YEAR BUILT'!K27</f>
-        <v/>
-      </c>
-      <c r="J42" s="50">
-        <f>'YEAR BUILT'!L27</f>
+      <c r="I42" s="51">
+        <f>'YEAR BUILT'!K28</f>
+        <v/>
+      </c>
+      <c r="J42" s="51">
+        <f>'YEAR BUILT'!L28</f>
         <v/>
       </c>
       <c r="K42" s="1" t="n"/>
@@ -8416,33 +8491,33 @@
     </row>
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="1" t="n"/>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="24" t="inlineStr">
         <is>
           <t>DAIKIN</t>
         </is>
       </c>
-      <c r="C43" s="50">
-        <f>'YEAR BUILT'!E27</f>
-        <v/>
-      </c>
-      <c r="D43" s="50">
-        <f>'YEAR BUILT'!F27</f>
+      <c r="C43" s="51">
+        <f>'YEAR BUILT'!E28</f>
+        <v/>
+      </c>
+      <c r="D43" s="51">
+        <f>'YEAR BUILT'!F28</f>
         <v/>
       </c>
       <c r="E43" s="1" t="n"/>
       <c r="F43" s="1" t="n"/>
       <c r="G43" s="1" t="n"/>
-      <c r="H43" s="23" t="inlineStr">
+      <c r="H43" s="24" t="inlineStr">
         <is>
           <t>DAIKIN</t>
         </is>
       </c>
-      <c r="I43" s="50">
-        <f>'YEAR BUILT'!M27</f>
-        <v/>
-      </c>
-      <c r="J43" s="50">
-        <f>'YEAR BUILT'!N27</f>
+      <c r="I43" s="51">
+        <f>'YEAR BUILT'!M28</f>
+        <v/>
+      </c>
+      <c r="J43" s="51">
+        <f>'YEAR BUILT'!N28</f>
         <v/>
       </c>
       <c r="K43" s="1" t="n"/>
@@ -8454,33 +8529,33 @@
     </row>
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="23" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>THERMO KING</t>
         </is>
       </c>
-      <c r="C44" s="50">
-        <f>'YEAR BUILT'!G27</f>
-        <v/>
-      </c>
-      <c r="D44" s="50">
-        <f>'YEAR BUILT'!H27</f>
+      <c r="C44" s="51">
+        <f>'YEAR BUILT'!G28</f>
+        <v/>
+      </c>
+      <c r="D44" s="51">
+        <f>'YEAR BUILT'!H28</f>
         <v/>
       </c>
       <c r="E44" s="1" t="n"/>
       <c r="F44" s="1" t="n"/>
       <c r="G44" s="1" t="n"/>
-      <c r="H44" s="23" t="inlineStr">
+      <c r="H44" s="24" t="inlineStr">
         <is>
           <t>THERMO KING</t>
         </is>
       </c>
-      <c r="I44" s="50">
-        <f>'YEAR BUILT'!O27</f>
-        <v/>
-      </c>
-      <c r="J44" s="50">
-        <f>'YEAR BUILT'!P27</f>
+      <c r="I44" s="51">
+        <f>'YEAR BUILT'!O28</f>
+        <v/>
+      </c>
+      <c r="J44" s="51">
+        <f>'YEAR BUILT'!P28</f>
         <v/>
       </c>
       <c r="K44" s="1" t="n"/>
@@ -8510,7 +8585,7 @@
     </row>
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="55" t="inlineStr">
+      <c r="B46" s="56" t="inlineStr">
         <is>
           <t>Full 2010-2026 Year x Brand x Size breakdown is on the YEAR BUILT sheet.</t>
         </is>
